--- a/assests/AmpTest claud4.xlsx
+++ b/assests/AmpTest claud4.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/toddanderson/Documents/claude projects/amplifinder/assests/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5737AF79-064A-BE4E-AC37-CA7E3EE2CCEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1143CEE-83BF-FB4D-819E-B2F63B70EBB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="740" yWindow="660" windowWidth="27640" windowHeight="16760" xr2:uid="{A2AA72AD-F933-604F-82A4-82C55EAB3989}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="647" uniqueCount="63">
   <si>
     <t xml:space="preserve">Deisign Centric </t>
   </si>
@@ -161,40 +161,70 @@
     <t>Suggested Subwoofers</t>
   </si>
   <si>
-    <t>MOS SUB or CSUB</t>
-  </si>
-  <si>
-    <t>CSUB or Blends800SUB</t>
-  </si>
-  <si>
-    <t>10 HDR, 10BPIG,S11, 12HDR or 12 BPIG</t>
-  </si>
-  <si>
-    <t>OSUB10 or OSUB12</t>
-  </si>
-  <si>
-    <t>CSUB</t>
-  </si>
-  <si>
-    <t>ASM210</t>
-  </si>
-  <si>
     <t>Architectural Speakers</t>
   </si>
   <si>
-    <t>D50</t>
-  </si>
-  <si>
-    <t>D60</t>
-  </si>
-  <si>
-    <t>D80</t>
-  </si>
-  <si>
-    <t>D100</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CSUB, DSUB6x2, or DSUB6 </t>
+    <t xml:space="preserve">Performance </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coverage </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MOS SUB </t>
+  </si>
+  <si>
+    <t>CSUB10</t>
+  </si>
+  <si>
+    <t>BLENDSSUB800</t>
+  </si>
+  <si>
+    <t>BLENDS CSUB10</t>
+  </si>
+  <si>
+    <t>D50 Series</t>
+  </si>
+  <si>
+    <t>D60 Series</t>
+  </si>
+  <si>
+    <t>D80 Series</t>
+  </si>
+  <si>
+    <t>D100 Series</t>
+  </si>
+  <si>
+    <t>AMD210</t>
+  </si>
+  <si>
+    <t>Coverage</t>
+  </si>
+  <si>
+    <t>10HDR</t>
+  </si>
+  <si>
+    <t>10BPIG</t>
+  </si>
+  <si>
+    <t>S11BP</t>
+  </si>
+  <si>
+    <t>12HDR</t>
+  </si>
+  <si>
+    <t>12BPIG</t>
+  </si>
+  <si>
+    <t>OSUB10</t>
+  </si>
+  <si>
+    <t>OSUB12</t>
+  </si>
+  <si>
+    <t>DSUB6x2</t>
+  </si>
+  <si>
+    <t>DSUB6F5K</t>
   </si>
 </sst>
 </file>
@@ -250,7 +280,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -259,6 +289,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -593,7 +627,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AEE2B7A6-BD38-654C-B9AA-5A01AA73CC18}">
-  <dimension ref="A1:L217"/>
+  <dimension ref="A1:O219"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="26.6640625" customWidth="1"/>
@@ -601,11 +635,13 @@
     <col min="3" max="3" width="26.6640625" customWidth="1"/>
     <col min="4" max="4" width="20.5" customWidth="1"/>
     <col min="5" max="5" width="26.6640625" customWidth="1"/>
-    <col min="6" max="6" width="27.6640625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="35.5" customWidth="1"/>
+    <col min="6" max="8" width="27.6640625" style="1" customWidth="1"/>
+    <col min="9" max="10" width="35.5" customWidth="1"/>
+    <col min="11" max="11" width="34.5" customWidth="1"/>
+    <col min="12" max="12" width="24.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>3</v>
       </c>
@@ -624,11 +660,16 @@
       <c r="F1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="4" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="J1" s="4"/>
+      <c r="K1" s="4"/>
+      <c r="L1" s="5"/>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -647,8 +688,24 @@
       <c r="F2" s="1">
         <v>250.1</v>
       </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="G2" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="L2" s="2"/>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1" t="s">
@@ -664,10 +721,13 @@
         <v>250.2</v>
       </c>
       <c r="G3" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+        <v>44</v>
+      </c>
+      <c r="J3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1" t="s">
@@ -682,8 +742,9 @@
       <c r="F4" s="1">
         <v>250.2</v>
       </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="G4"/>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1" t="s">
@@ -699,10 +760,13 @@
         <v>250.4</v>
       </c>
       <c r="G5" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+        <v>44</v>
+      </c>
+      <c r="J5" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="C6" s="1" t="s">
@@ -718,10 +782,13 @@
         <v>250.4</v>
       </c>
       <c r="G6" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+        <v>44</v>
+      </c>
+      <c r="J6" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1" t="s">
@@ -736,8 +803,9 @@
       <c r="F7" s="1">
         <v>250.4</v>
       </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="G7"/>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1" t="s">
@@ -753,10 +821,13 @@
         <v>250.4</v>
       </c>
       <c r="G8" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+        <v>44</v>
+      </c>
+      <c r="J8" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1" t="s">
@@ -772,10 +843,13 @@
         <v>250.4</v>
       </c>
       <c r="G9" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+        <v>44</v>
+      </c>
+      <c r="J9" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1" t="s">
@@ -790,8 +864,9 @@
       <c r="F10" s="1">
         <v>250.4</v>
       </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="G10"/>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>21</v>
       </c>
@@ -805,10 +880,13 @@
         <v>8</v>
       </c>
       <c r="G11" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+        <v>44</v>
+      </c>
+      <c r="J11" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>21</v>
       </c>
@@ -822,13 +900,16 @@
         <v>9</v>
       </c>
       <c r="G12" t="s">
-        <v>41</v>
-      </c>
-      <c r="J12" s="1"/>
-      <c r="K12" s="1"/>
-      <c r="L12" s="1"/>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+        <v>44</v>
+      </c>
+      <c r="J12" t="s">
+        <v>45</v>
+      </c>
+      <c r="M12" s="1"/>
+      <c r="N12" s="1"/>
+      <c r="O12" s="1"/>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B13" t="s">
         <v>10</v>
       </c>
@@ -844,8 +925,9 @@
       <c r="F13" s="1">
         <v>125.1</v>
       </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="G13"/>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>21</v>
       </c>
@@ -859,10 +941,13 @@
         <v>250.2</v>
       </c>
       <c r="G14" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+        <v>46</v>
+      </c>
+      <c r="J14" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>21</v>
       </c>
@@ -875,8 +960,9 @@
       <c r="F15" s="1">
         <v>125.2</v>
       </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="G15"/>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C16" s="1" t="s">
         <v>21</v>
       </c>
@@ -890,11 +976,13 @@
         <v>250.4</v>
       </c>
       <c r="G16" t="s">
-        <v>42</v>
-      </c>
-      <c r="I16" s="1"/>
-    </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.2">
+        <v>46</v>
+      </c>
+      <c r="J16" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="17" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>21</v>
       </c>
@@ -908,10 +996,14 @@
         <v>250.4</v>
       </c>
       <c r="G17" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="18" spans="2:7" x14ac:dyDescent="0.2">
+        <v>46</v>
+      </c>
+      <c r="J17" t="s">
+        <v>47</v>
+      </c>
+      <c r="L17" s="1"/>
+    </row>
+    <row r="18" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>21</v>
       </c>
@@ -924,8 +1016,9 @@
       <c r="F18" s="1">
         <v>125.4</v>
       </c>
-    </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="G18"/>
+    </row>
+    <row r="19" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>21</v>
       </c>
@@ -939,10 +1032,13 @@
         <v>250.4</v>
       </c>
       <c r="G19" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="20" spans="2:7" x14ac:dyDescent="0.2">
+        <v>46</v>
+      </c>
+      <c r="J19" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="20" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>21</v>
       </c>
@@ -956,10 +1052,13 @@
         <v>250.4</v>
       </c>
       <c r="G20" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="21" spans="2:7" x14ac:dyDescent="0.2">
+        <v>46</v>
+      </c>
+      <c r="J20" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="21" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>21</v>
       </c>
@@ -972,8 +1071,9 @@
       <c r="F21" s="1">
         <v>125.4</v>
       </c>
-    </row>
-    <row r="22" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="G21"/>
+    </row>
+    <row r="22" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>21</v>
       </c>
@@ -987,10 +1087,13 @@
         <v>11</v>
       </c>
       <c r="G22" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="23" spans="2:7" x14ac:dyDescent="0.2">
+        <v>46</v>
+      </c>
+      <c r="J22" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="23" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>21</v>
       </c>
@@ -1003,11 +1106,14 @@
       <c r="F23" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="G23" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="24" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="G23" t="s">
+        <v>46</v>
+      </c>
+      <c r="J23" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="24" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B24" t="s">
         <v>13</v>
       </c>
@@ -1024,8 +1130,9 @@
         <v>250.1</v>
       </c>
       <c r="G24" s="3"/>
-    </row>
-    <row r="25" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="I24" s="3"/>
+    </row>
+    <row r="25" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>21</v>
       </c>
@@ -1038,11 +1145,14 @@
       <c r="F25" s="1">
         <v>250.2</v>
       </c>
-      <c r="G25" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="26" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="G25" t="s">
+        <v>46</v>
+      </c>
+      <c r="J25" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="26" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1055,8 +1165,9 @@
       <c r="F26" s="1">
         <v>250.2</v>
       </c>
-    </row>
-    <row r="27" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="G26"/>
+    </row>
+    <row r="27" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
@@ -1069,11 +1180,14 @@
       <c r="F27" s="1">
         <v>250.4</v>
       </c>
-      <c r="G27" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="28" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="G27" t="s">
+        <v>46</v>
+      </c>
+      <c r="J27" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="28" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>21</v>
       </c>
@@ -1086,11 +1200,14 @@
       <c r="F28" s="1">
         <v>250.4</v>
       </c>
-      <c r="G28" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="29" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="G28" t="s">
+        <v>46</v>
+      </c>
+      <c r="J28" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="29" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>21</v>
       </c>
@@ -1103,8 +1220,9 @@
       <c r="F29" s="1">
         <v>250.4</v>
       </c>
-    </row>
-    <row r="30" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="G29"/>
+    </row>
+    <row r="30" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>21</v>
       </c>
@@ -1117,11 +1235,14 @@
       <c r="F30" s="1">
         <v>250.4</v>
       </c>
-      <c r="G30" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="31" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="G30" t="s">
+        <v>46</v>
+      </c>
+      <c r="J30" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="31" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>21</v>
       </c>
@@ -1134,11 +1255,14 @@
       <c r="F31" s="1">
         <v>250.4</v>
       </c>
-      <c r="G31" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="32" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="G31" t="s">
+        <v>46</v>
+      </c>
+      <c r="J31" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="32" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>21</v>
       </c>
@@ -1151,8 +1275,9 @@
       <c r="F32" s="1">
         <v>250.4</v>
       </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G32"/>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>21</v>
       </c>
@@ -1165,11 +1290,14 @@
       <c r="F33" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G33" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G33" t="s">
+        <v>46</v>
+      </c>
+      <c r="J33" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>21</v>
       </c>
@@ -1182,11 +1310,14 @@
       <c r="F34" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G34" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G34" t="s">
+        <v>46</v>
+      </c>
+      <c r="J34" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B35" t="s">
         <v>15</v>
       </c>
@@ -1203,8 +1334,9 @@
         <v>250.1</v>
       </c>
       <c r="G35" s="3"/>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="I35" s="3"/>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.2">
       <c r="C36" s="1" t="s">
         <v>21</v>
       </c>
@@ -1217,11 +1349,14 @@
       <c r="F36" s="1">
         <v>250.2</v>
       </c>
-      <c r="G36" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G36" t="s">
+        <v>46</v>
+      </c>
+      <c r="J36" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.2">
       <c r="C37" s="1" t="s">
         <v>21</v>
       </c>
@@ -1235,8 +1370,9 @@
         <v>250.2</v>
       </c>
       <c r="G37" s="3"/>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="I37" s="3"/>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>21</v>
       </c>
@@ -1249,11 +1385,14 @@
       <c r="F38" s="1">
         <v>250.4</v>
       </c>
-      <c r="G38" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G38" t="s">
+        <v>46</v>
+      </c>
+      <c r="J38" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>21</v>
       </c>
@@ -1266,11 +1405,14 @@
       <c r="F39" s="1">
         <v>250.4</v>
       </c>
-      <c r="G39" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G39" t="s">
+        <v>46</v>
+      </c>
+      <c r="J39" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>21</v>
       </c>
@@ -1284,8 +1426,9 @@
         <v>250.4</v>
       </c>
       <c r="G40" s="3"/>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="I40" s="3"/>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>21</v>
       </c>
@@ -1298,11 +1441,14 @@
       <c r="F41" s="1">
         <v>250.4</v>
       </c>
-      <c r="G41" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G41" t="s">
+        <v>46</v>
+      </c>
+      <c r="J41" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>21</v>
       </c>
@@ -1315,11 +1461,14 @@
       <c r="F42" s="1">
         <v>250.4</v>
       </c>
-      <c r="G42" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G42" t="s">
+        <v>46</v>
+      </c>
+      <c r="J42" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>21</v>
       </c>
@@ -1333,8 +1482,9 @@
         <v>250.4</v>
       </c>
       <c r="G43" s="3"/>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="I43" s="3"/>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>21</v>
       </c>
@@ -1348,10 +1498,13 @@
         <v>8</v>
       </c>
       <c r="G44" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
+        <v>46</v>
+      </c>
+      <c r="J44" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>21</v>
       </c>
@@ -1365,10 +1518,13 @@
         <v>9</v>
       </c>
       <c r="G45" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
+        <v>46</v>
+      </c>
+      <c r="J45" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>1</v>
       </c>
@@ -1387,8 +1543,9 @@
       <c r="F46" s="1">
         <v>250.1</v>
       </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G46"/>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>17</v>
       </c>
@@ -1402,7 +1559,7 @@
         <v>250.1</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>16</v>
       </c>
@@ -1415,11 +1572,23 @@
       <c r="F48" s="1">
         <v>250.1</v>
       </c>
-      <c r="G48" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="49" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="G48" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="H48" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="I48" t="s">
+        <v>56</v>
+      </c>
+      <c r="J48" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="K48" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="49" spans="2:11" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>17</v>
       </c>
@@ -1432,11 +1601,20 @@
       <c r="F49" s="1">
         <v>1000.2</v>
       </c>
-      <c r="G49" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="50" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="G49" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="I49" t="s">
+        <v>56</v>
+      </c>
+      <c r="J49" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="K49" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="50" spans="2:11" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>16</v>
       </c>
@@ -1450,7 +1628,7 @@
         <v>1000.1</v>
       </c>
     </row>
-    <row r="51" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="51" spans="2:11" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>17</v>
       </c>
@@ -1464,7 +1642,7 @@
         <v>1000.2</v>
       </c>
     </row>
-    <row r="52" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="52" spans="2:11" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>16</v>
       </c>
@@ -1477,11 +1655,23 @@
       <c r="F52" s="1">
         <v>1000.4</v>
       </c>
-      <c r="G52" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="53" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="G52" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="H52" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="I52" t="s">
+        <v>56</v>
+      </c>
+      <c r="J52" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="K52" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="53" spans="2:11" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>17</v>
       </c>
@@ -1494,11 +1684,23 @@
       <c r="F53" s="1">
         <v>1000.4</v>
       </c>
-      <c r="G53" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="54" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="G53" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="H53" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="I53" t="s">
+        <v>56</v>
+      </c>
+      <c r="J53" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="K53" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="54" spans="2:11" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>16</v>
       </c>
@@ -1511,11 +1713,23 @@
       <c r="F54" s="1">
         <v>1000.4</v>
       </c>
-      <c r="G54" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="55" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="G54" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="H54" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="I54" t="s">
+        <v>56</v>
+      </c>
+      <c r="J54" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="K54" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="55" spans="2:11" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>17</v>
       </c>
@@ -1528,11 +1742,23 @@
       <c r="F55" s="1">
         <v>1000.4</v>
       </c>
-      <c r="G55" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="56" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="G55" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="H55" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="I55" t="s">
+        <v>56</v>
+      </c>
+      <c r="J55" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="K55" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="56" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B56" t="s">
         <v>14</v>
       </c>
@@ -1549,7 +1775,7 @@
         <v>250.1</v>
       </c>
     </row>
-    <row r="57" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="57" spans="2:11" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>17</v>
       </c>
@@ -1563,7 +1789,7 @@
         <v>250.1</v>
       </c>
     </row>
-    <row r="58" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="58" spans="2:11" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>16</v>
       </c>
@@ -1576,11 +1802,23 @@
       <c r="F58" s="1">
         <v>250.1</v>
       </c>
-      <c r="G58" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="59" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="G58" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="H58" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="I58" t="s">
+        <v>56</v>
+      </c>
+      <c r="J58" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="K58" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="59" spans="2:11" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>17</v>
       </c>
@@ -1593,11 +1831,23 @@
       <c r="F59" s="1">
         <v>1000.2</v>
       </c>
-      <c r="G59" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="60" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="G59" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="H59" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="I59" t="s">
+        <v>56</v>
+      </c>
+      <c r="J59" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="K59" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="60" spans="2:11" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>16</v>
       </c>
@@ -1611,7 +1861,7 @@
         <v>1000.1</v>
       </c>
     </row>
-    <row r="61" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="61" spans="2:11" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>17</v>
       </c>
@@ -1625,7 +1875,7 @@
         <v>1000.2</v>
       </c>
     </row>
-    <row r="62" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="62" spans="2:11" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>16</v>
       </c>
@@ -1638,11 +1888,23 @@
       <c r="F62" s="1">
         <v>1000.4</v>
       </c>
-      <c r="G62" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="63" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="G62" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="H62" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="I62" t="s">
+        <v>56</v>
+      </c>
+      <c r="J62" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="K62" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="63" spans="2:11" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>17</v>
       </c>
@@ -1655,11 +1917,23 @@
       <c r="F63" s="1">
         <v>1000.4</v>
       </c>
-      <c r="G63" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="64" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="G63" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="H63" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="I63" t="s">
+        <v>56</v>
+      </c>
+      <c r="J63" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="K63" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="64" spans="2:11" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>16</v>
       </c>
@@ -1672,11 +1946,23 @@
       <c r="F64" s="1">
         <v>1000.4</v>
       </c>
-      <c r="G64" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="65" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="G64" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="H64" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="I64" t="s">
+        <v>56</v>
+      </c>
+      <c r="J64" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="K64" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="65" spans="2:11" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>17</v>
       </c>
@@ -1689,11 +1975,23 @@
       <c r="F65" s="1">
         <v>1000.4</v>
       </c>
-      <c r="G65" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="66" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="G65" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="H65" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="I65" t="s">
+        <v>56</v>
+      </c>
+      <c r="J65" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="K65" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="66" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B66" t="s">
         <v>19</v>
       </c>
@@ -1710,7 +2008,7 @@
         <v>250.1</v>
       </c>
     </row>
-    <row r="67" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:11" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>17</v>
       </c>
@@ -1724,7 +2022,7 @@
         <v>250.1</v>
       </c>
     </row>
-    <row r="68" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:11" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>16</v>
       </c>
@@ -1737,11 +2035,23 @@
       <c r="F68" s="1">
         <v>250.1</v>
       </c>
-      <c r="G68" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="69" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="G68" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="H68" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="I68" t="s">
+        <v>56</v>
+      </c>
+      <c r="J68" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="K68" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="69" spans="2:11" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>17</v>
       </c>
@@ -1754,11 +2064,23 @@
       <c r="F69" s="1">
         <v>1000.2</v>
       </c>
-      <c r="G69" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="70" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="G69" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="H69" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="I69" t="s">
+        <v>56</v>
+      </c>
+      <c r="J69" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="K69" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="70" spans="2:11" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>16</v>
       </c>
@@ -1772,7 +2094,7 @@
         <v>1000.1</v>
       </c>
     </row>
-    <row r="71" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:11" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>17</v>
       </c>
@@ -1786,7 +2108,7 @@
         <v>1000.2</v>
       </c>
     </row>
-    <row r="72" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:11" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>16</v>
       </c>
@@ -1799,11 +2121,23 @@
       <c r="F72" s="1">
         <v>1000.4</v>
       </c>
-      <c r="G72" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="73" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="G72" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="H72" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="I72" t="s">
+        <v>56</v>
+      </c>
+      <c r="J72" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="K72" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="73" spans="2:11" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>17</v>
       </c>
@@ -1816,11 +2150,23 @@
       <c r="F73" s="1">
         <v>1000.4</v>
       </c>
-      <c r="G73" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="74" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="G73" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="H73" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="I73" t="s">
+        <v>56</v>
+      </c>
+      <c r="J73" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="K73" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="74" spans="2:11" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>16</v>
       </c>
@@ -1833,11 +2179,23 @@
       <c r="F74" s="1">
         <v>1000.4</v>
       </c>
-      <c r="G74" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="75" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="G74" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="H74" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="I74" t="s">
+        <v>56</v>
+      </c>
+      <c r="J74" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="K74" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="75" spans="2:11" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>17</v>
       </c>
@@ -1850,11 +2208,23 @@
       <c r="F75" s="1">
         <v>1000.4</v>
       </c>
-      <c r="G75" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="76" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="G75" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="H75" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="I75" t="s">
+        <v>56</v>
+      </c>
+      <c r="J75" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="K75" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="76" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B76" t="s">
         <v>20</v>
       </c>
@@ -1870,8 +2240,9 @@
       <c r="F76" s="1">
         <v>1000.2</v>
       </c>
-    </row>
-    <row r="77" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="J76" s="1"/>
+    </row>
+    <row r="77" spans="2:11" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>17</v>
       </c>
@@ -1885,7 +2256,7 @@
         <v>1000.2</v>
       </c>
     </row>
-    <row r="78" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="78" spans="2:11" x14ac:dyDescent="0.2">
       <c r="C78" s="1" t="s">
         <v>16</v>
       </c>
@@ -1899,7 +2270,7 @@
         <v>1000.2</v>
       </c>
     </row>
-    <row r="79" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:11" x14ac:dyDescent="0.2">
       <c r="C79" s="1" t="s">
         <v>17</v>
       </c>
@@ -1913,7 +2284,7 @@
         <v>1000.2</v>
       </c>
     </row>
-    <row r="80" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:11" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>16</v>
       </c>
@@ -1927,7 +2298,7 @@
         <v>1000.2</v>
       </c>
     </row>
-    <row r="81" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="81" spans="2:6" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>17</v>
       </c>
@@ -1941,7 +2312,7 @@
         <v>1000.2</v>
       </c>
     </row>
-    <row r="82" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="82" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B82" t="s">
         <v>22</v>
       </c>
@@ -1958,7 +2329,7 @@
         <v>1000.2</v>
       </c>
     </row>
-    <row r="83" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="83" spans="2:6" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>17</v>
       </c>
@@ -1972,7 +2343,7 @@
         <v>1000.2</v>
       </c>
     </row>
-    <row r="84" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="84" spans="2:6" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>16</v>
       </c>
@@ -1986,7 +2357,7 @@
         <v>1000.2</v>
       </c>
     </row>
-    <row r="85" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="85" spans="2:6" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>17</v>
       </c>
@@ -2000,7 +2371,7 @@
         <v>1000.2</v>
       </c>
     </row>
-    <row r="86" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="86" spans="2:6" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>16</v>
       </c>
@@ -2014,7 +2385,7 @@
         <v>1000.2</v>
       </c>
     </row>
-    <row r="87" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="87" spans="2:6" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>17</v>
       </c>
@@ -2028,7 +2399,7 @@
         <v>1000.2</v>
       </c>
     </row>
-    <row r="88" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="88" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B88" t="s">
         <v>23</v>
       </c>
@@ -2045,7 +2416,7 @@
         <v>1000.2</v>
       </c>
     </row>
-    <row r="89" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="89" spans="2:6" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>17</v>
       </c>
@@ -2059,7 +2430,7 @@
         <v>1000.2</v>
       </c>
     </row>
-    <row r="90" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="90" spans="2:6" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>16</v>
       </c>
@@ -2073,7 +2444,7 @@
         <v>1000.2</v>
       </c>
     </row>
-    <row r="91" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="91" spans="2:6" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>17</v>
       </c>
@@ -2087,7 +2458,7 @@
         <v>1000.2</v>
       </c>
     </row>
-    <row r="92" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="92" spans="2:6" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>16</v>
       </c>
@@ -2101,7 +2472,7 @@
         <v>1000.2</v>
       </c>
     </row>
-    <row r="93" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="93" spans="2:6" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>17</v>
       </c>
@@ -2115,38 +2486,38 @@
         <v>1000.2</v>
       </c>
     </row>
-    <row r="94" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B94" t="s">
-        <v>24</v>
-      </c>
+    <row r="94" spans="2:6" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D94" s="1">
-        <v>2</v>
-      </c>
-      <c r="E94" s="1">
-        <v>0</v>
+        <v>8</v>
+      </c>
+      <c r="E94" s="1" t="s">
+        <v>21</v>
       </c>
       <c r="F94" s="1">
-        <v>250.1</v>
-      </c>
-    </row>
-    <row r="95" spans="2:7" x14ac:dyDescent="0.2">
+        <v>1000.4</v>
+      </c>
+    </row>
+    <row r="95" spans="2:6" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D95" s="1">
-        <v>2</v>
-      </c>
-      <c r="E95" s="1">
-        <v>0</v>
+        <v>8</v>
+      </c>
+      <c r="E95" s="1" t="s">
+        <v>21</v>
       </c>
       <c r="F95" s="1">
-        <v>250.1</v>
-      </c>
-    </row>
-    <row r="96" spans="2:7" x14ac:dyDescent="0.2">
+        <v>1000.4</v>
+      </c>
+    </row>
+    <row r="96" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B96" t="s">
+        <v>24</v>
+      </c>
       <c r="C96" s="1" t="s">
         <v>16</v>
       </c>
@@ -2154,16 +2525,13 @@
         <v>2</v>
       </c>
       <c r="E96" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F96" s="1">
         <v>250.1</v>
       </c>
-      <c r="G96" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="97" spans="2:7" x14ac:dyDescent="0.2">
+    </row>
+    <row r="97" spans="2:11" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>17</v>
       </c>
@@ -2171,44 +2539,65 @@
         <v>2</v>
       </c>
       <c r="E97" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F97" s="1">
-        <v>1000.2</v>
-      </c>
-      <c r="G97" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="98" spans="2:7" x14ac:dyDescent="0.2">
+        <v>250.1</v>
+      </c>
+    </row>
+    <row r="98" spans="2:11" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D98" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E98" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F98" s="1">
-        <v>1000.1</v>
-      </c>
-    </row>
-    <row r="99" spans="2:7" x14ac:dyDescent="0.2">
+        <v>250.1</v>
+      </c>
+      <c r="G98" t="s">
+        <v>59</v>
+      </c>
+      <c r="H98" t="s">
+        <v>60</v>
+      </c>
+      <c r="J98" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="K98" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="99" spans="2:11" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D99" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E99" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F99" s="1">
         <v>1000.2</v>
       </c>
-    </row>
-    <row r="100" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="G99" t="s">
+        <v>59</v>
+      </c>
+      <c r="H99" t="s">
+        <v>60</v>
+      </c>
+      <c r="J99" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="K99" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="100" spans="2:11" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>16</v>
       </c>
@@ -2216,16 +2605,14 @@
         <v>4</v>
       </c>
       <c r="E100" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F100" s="1">
-        <v>1000.4</v>
-      </c>
-      <c r="G100" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="101" spans="2:7" x14ac:dyDescent="0.2">
+        <v>1000.1</v>
+      </c>
+      <c r="H100"/>
+    </row>
+    <row r="101" spans="2:11" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>17</v>
       </c>
@@ -2233,16 +2620,14 @@
         <v>4</v>
       </c>
       <c r="E101" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F101" s="1">
-        <v>1000.4</v>
-      </c>
-      <c r="G101" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="102" spans="2:7" x14ac:dyDescent="0.2">
+        <v>1000.2</v>
+      </c>
+      <c r="H101"/>
+    </row>
+    <row r="102" spans="2:11" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>16</v>
       </c>
@@ -2250,16 +2635,25 @@
         <v>4</v>
       </c>
       <c r="E102" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F102" s="1">
         <v>1000.4</v>
       </c>
       <c r="G102" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="103" spans="2:7" x14ac:dyDescent="0.2">
+        <v>59</v>
+      </c>
+      <c r="H102" t="s">
+        <v>60</v>
+      </c>
+      <c r="J102" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="K102" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="103" spans="2:11" x14ac:dyDescent="0.2">
       <c r="C103" s="1" t="s">
         <v>17</v>
       </c>
@@ -2267,44 +2661,69 @@
         <v>4</v>
       </c>
       <c r="E103" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F103" s="1">
         <v>1000.4</v>
       </c>
-    </row>
-    <row r="104" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B104" t="s">
-        <v>25</v>
-      </c>
+      <c r="G103" t="s">
+        <v>59</v>
+      </c>
+      <c r="H103" t="s">
+        <v>60</v>
+      </c>
+      <c r="J103" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="K103" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="104" spans="2:11" x14ac:dyDescent="0.2">
       <c r="C104" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D104" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E104" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F104" s="1">
-        <v>250.1</v>
-      </c>
-    </row>
-    <row r="105" spans="2:7" x14ac:dyDescent="0.2">
+        <v>1000.4</v>
+      </c>
+      <c r="G104" t="s">
+        <v>59</v>
+      </c>
+      <c r="H104" t="s">
+        <v>60</v>
+      </c>
+      <c r="J104" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="K104" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="105" spans="2:11" x14ac:dyDescent="0.2">
       <c r="C105" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D105" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E105" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F105" s="1">
-        <v>250.1</v>
-      </c>
-    </row>
-    <row r="106" spans="2:7" x14ac:dyDescent="0.2">
+        <v>1000.4</v>
+      </c>
+      <c r="H105"/>
+    </row>
+    <row r="106" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B106" t="s">
+        <v>25</v>
+      </c>
       <c r="C106" s="1" t="s">
         <v>16</v>
       </c>
@@ -2312,16 +2731,14 @@
         <v>2</v>
       </c>
       <c r="E106" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F106" s="1">
         <v>250.1</v>
       </c>
-      <c r="G106" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="107" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="H106"/>
+    </row>
+    <row r="107" spans="2:11" x14ac:dyDescent="0.2">
       <c r="C107" s="1" t="s">
         <v>17</v>
       </c>
@@ -2329,44 +2746,66 @@
         <v>2</v>
       </c>
       <c r="E107" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F107" s="1">
-        <v>1000.2</v>
-      </c>
-      <c r="G107" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="108" spans="2:7" x14ac:dyDescent="0.2">
+        <v>250.1</v>
+      </c>
+      <c r="H107"/>
+    </row>
+    <row r="108" spans="2:11" x14ac:dyDescent="0.2">
       <c r="C108" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D108" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E108" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F108" s="1">
-        <v>1000.1</v>
-      </c>
-    </row>
-    <row r="109" spans="2:7" x14ac:dyDescent="0.2">
+        <v>250.1</v>
+      </c>
+      <c r="G108" t="s">
+        <v>59</v>
+      </c>
+      <c r="H108" t="s">
+        <v>60</v>
+      </c>
+      <c r="J108" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="K108" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="109" spans="2:11" x14ac:dyDescent="0.2">
       <c r="C109" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D109" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E109" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F109" s="1">
         <v>1000.2</v>
       </c>
-    </row>
-    <row r="110" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="G109" t="s">
+        <v>59</v>
+      </c>
+      <c r="H109" t="s">
+        <v>60</v>
+      </c>
+      <c r="J109" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="K109" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="110" spans="2:11" x14ac:dyDescent="0.2">
       <c r="C110" s="1" t="s">
         <v>16</v>
       </c>
@@ -2374,16 +2813,14 @@
         <v>4</v>
       </c>
       <c r="E110" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F110" s="1">
-        <v>1000.4</v>
-      </c>
-      <c r="G110" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="111" spans="2:7" x14ac:dyDescent="0.2">
+        <v>1000.1</v>
+      </c>
+      <c r="H110"/>
+    </row>
+    <row r="111" spans="2:11" x14ac:dyDescent="0.2">
       <c r="C111" s="1" t="s">
         <v>17</v>
       </c>
@@ -2391,16 +2828,14 @@
         <v>4</v>
       </c>
       <c r="E111" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F111" s="1">
-        <v>1000.4</v>
-      </c>
-      <c r="G111" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="112" spans="2:7" x14ac:dyDescent="0.2">
+        <v>1000.2</v>
+      </c>
+      <c r="H111"/>
+    </row>
+    <row r="112" spans="2:11" x14ac:dyDescent="0.2">
       <c r="C112" s="1" t="s">
         <v>16</v>
       </c>
@@ -2408,16 +2843,25 @@
         <v>4</v>
       </c>
       <c r="E112" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F112" s="1">
         <v>1000.4</v>
       </c>
       <c r="G112" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.2">
+        <v>59</v>
+      </c>
+      <c r="H112" t="s">
+        <v>60</v>
+      </c>
+      <c r="J112" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="K112" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="113" spans="1:11" x14ac:dyDescent="0.2">
       <c r="C113" s="1" t="s">
         <v>17</v>
       </c>
@@ -2425,98 +2869,147 @@
         <v>4</v>
       </c>
       <c r="E113" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F113" s="1">
         <v>1000.4</v>
       </c>
       <c r="G113" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B114" t="s">
+        <v>59</v>
+      </c>
+      <c r="H113" t="s">
+        <v>60</v>
+      </c>
+      <c r="J113" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="K113" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="114" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="C114" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D114" s="1">
+        <v>4</v>
+      </c>
+      <c r="E114" s="1">
+        <v>2</v>
+      </c>
+      <c r="F114" s="1">
+        <v>1000.4</v>
+      </c>
+      <c r="G114" t="s">
+        <v>59</v>
+      </c>
+      <c r="H114" t="s">
+        <v>60</v>
+      </c>
+      <c r="J114" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="K114" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="115" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="C115" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D115" s="1">
+        <v>4</v>
+      </c>
+      <c r="E115" s="1">
+        <v>2</v>
+      </c>
+      <c r="F115" s="1">
+        <v>1000.4</v>
+      </c>
+      <c r="G115" t="s">
+        <v>59</v>
+      </c>
+      <c r="H115" t="s">
+        <v>60</v>
+      </c>
+      <c r="J115" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="K115" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="116" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="B116" t="s">
         <v>26</v>
       </c>
-      <c r="C114" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D114" s="1">
-        <v>2</v>
-      </c>
-      <c r="E114" s="1">
-        <v>0</v>
-      </c>
-      <c r="F114" s="1">
+      <c r="C116" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D116" s="1">
+        <v>2</v>
+      </c>
+      <c r="E116" s="1">
+        <v>0</v>
+      </c>
+      <c r="F116" s="1">
         <v>250.1</v>
       </c>
-    </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="C115" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D115" s="1">
-        <v>2</v>
-      </c>
-      <c r="E115" s="1">
-        <v>1</v>
-      </c>
-      <c r="F115" s="1">
-        <v>250.2</v>
-      </c>
-      <c r="G115" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="C116" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D116" s="1">
-        <v>2</v>
-      </c>
-      <c r="E116" s="1">
-        <v>2</v>
-      </c>
-      <c r="F116" s="1">
-        <v>250.4</v>
-      </c>
-      <c r="G116" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H116"/>
+    </row>
+    <row r="117" spans="1:11" x14ac:dyDescent="0.2">
       <c r="C117" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D117" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E117" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F117" s="1">
         <v>250.2</v>
       </c>
-    </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G117" t="s">
+        <v>59</v>
+      </c>
+      <c r="H117" t="s">
+        <v>60</v>
+      </c>
+      <c r="J117" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="K117" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="118" spans="1:11" x14ac:dyDescent="0.2">
       <c r="C118" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D118" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E118" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F118" s="1">
         <v>250.4</v>
       </c>
       <c r="G118" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.2">
+        <v>59</v>
+      </c>
+      <c r="H118" t="s">
+        <v>60</v>
+      </c>
+      <c r="J118" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="K118" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="119" spans="1:11" x14ac:dyDescent="0.2">
       <c r="C119" s="1" t="s">
         <v>21</v>
       </c>
@@ -2524,55 +3017,77 @@
         <v>4</v>
       </c>
       <c r="E119" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F119" s="1">
-        <v>250.4</v>
-      </c>
-      <c r="G119" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A120" t="s">
+        <v>250.2</v>
+      </c>
+      <c r="H119"/>
+    </row>
+    <row r="120" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="C120" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D120" s="1">
+        <v>4</v>
+      </c>
+      <c r="E120" s="1">
+        <v>1</v>
+      </c>
+      <c r="F120" s="1">
+        <v>250.4</v>
+      </c>
+      <c r="G120" t="s">
+        <v>59</v>
+      </c>
+      <c r="H120" t="s">
+        <v>60</v>
+      </c>
+      <c r="J120" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="K120" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="121" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="C121" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D121" s="1">
+        <v>4</v>
+      </c>
+      <c r="E121" s="1">
+        <v>2</v>
+      </c>
+      <c r="F121" s="1">
+        <v>250.4</v>
+      </c>
+      <c r="G121" t="s">
+        <v>59</v>
+      </c>
+      <c r="H121" t="s">
+        <v>60</v>
+      </c>
+      <c r="J121" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="K121" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="122" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A122" t="s">
         <v>27</v>
       </c>
-      <c r="B120" t="s">
+      <c r="B122" t="s">
         <v>28</v>
       </c>
-      <c r="C120" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D120" s="1" t="s">
+      <c r="C122" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D122" s="1" t="s">
         <v>29</v>
-      </c>
-      <c r="E120" s="1">
-        <v>0</v>
-      </c>
-      <c r="F120" s="1">
-        <v>125.1</v>
-      </c>
-    </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="C121" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D121" t="s">
-        <v>30</v>
-      </c>
-      <c r="E121" s="1">
-        <v>0</v>
-      </c>
-      <c r="F121" s="1">
-        <v>125.2</v>
-      </c>
-    </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="C122" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D122" t="s">
-        <v>31</v>
       </c>
       <c r="E122" s="1">
         <v>0</v>
@@ -2580,191 +3095,197 @@
       <c r="F122" s="1">
         <v>125.1</v>
       </c>
-    </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G122"/>
+      <c r="H122"/>
+      <c r="J122" s="1"/>
+    </row>
+    <row r="123" spans="1:11" x14ac:dyDescent="0.2">
       <c r="C123" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D123" s="1" t="s">
+      <c r="D123" t="s">
+        <v>30</v>
+      </c>
+      <c r="E123" s="1">
+        <v>0</v>
+      </c>
+      <c r="F123" s="1">
+        <v>125.2</v>
+      </c>
+    </row>
+    <row r="124" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="C124" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D124" t="s">
+        <v>31</v>
+      </c>
+      <c r="E124" s="1">
+        <v>0</v>
+      </c>
+      <c r="F124" s="1">
+        <v>125.1</v>
+      </c>
+    </row>
+    <row r="125" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="C125" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D125" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E123" s="1">
-        <v>1</v>
-      </c>
-      <c r="F123" s="1">
+      <c r="E125" s="1">
+        <v>1</v>
+      </c>
+      <c r="F125" s="1">
         <v>250.2</v>
-      </c>
-      <c r="G123" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="C124" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D124" t="s">
-        <v>30</v>
-      </c>
-      <c r="E124" s="1">
-        <v>1</v>
-      </c>
-      <c r="F124" s="1">
-        <v>250.4</v>
-      </c>
-      <c r="G124" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="C125" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D125" t="s">
-        <v>31</v>
-      </c>
-      <c r="E125" s="1">
-        <v>1</v>
-      </c>
-      <c r="F125" s="1">
-        <v>250.4</v>
       </c>
       <c r="G125" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B126" t="s">
+    <row r="126" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="C126" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D126" t="s">
+        <v>30</v>
+      </c>
+      <c r="E126" s="1">
+        <v>1</v>
+      </c>
+      <c r="F126" s="1">
+        <v>250.4</v>
+      </c>
+      <c r="G126" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="127" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="C127" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D127" t="s">
+        <v>31</v>
+      </c>
+      <c r="E127" s="1">
+        <v>1</v>
+      </c>
+      <c r="F127" s="1">
+        <v>250.4</v>
+      </c>
+      <c r="G127" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="128" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="B128" t="s">
         <v>32</v>
       </c>
-      <c r="C126" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D126" s="1" t="s">
+      <c r="C128" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D128" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E126" s="1">
-        <v>0</v>
-      </c>
-      <c r="F126" s="1">
+      <c r="E128" s="1">
+        <v>0</v>
+      </c>
+      <c r="F128" s="1">
         <v>250.1</v>
       </c>
-    </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="C127" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D127" t="s">
+      <c r="G128"/>
+    </row>
+    <row r="129" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="C129" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D129" t="s">
         <v>30</v>
       </c>
-      <c r="E127" s="1">
-        <v>0</v>
-      </c>
-      <c r="F127" s="1">
+      <c r="E129" s="1">
+        <v>0</v>
+      </c>
+      <c r="F129" s="1">
         <v>250.1</v>
       </c>
-    </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="C128" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D128" t="s">
+      <c r="G129"/>
+    </row>
+    <row r="130" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="C130" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D130" t="s">
         <v>31</v>
       </c>
-      <c r="E128" s="1">
-        <v>0</v>
-      </c>
-      <c r="F128" s="1">
-        <v>250.4</v>
-      </c>
-    </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="C129" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D129" s="1" t="s">
+      <c r="E130" s="1">
+        <v>0</v>
+      </c>
+      <c r="F130" s="1">
+        <v>250.4</v>
+      </c>
+      <c r="G130"/>
+    </row>
+    <row r="131" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="C131" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D131" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E129" s="1">
-        <v>1</v>
-      </c>
-      <c r="F129" s="1">
+      <c r="E131" s="1">
+        <v>1</v>
+      </c>
+      <c r="F131" s="1">
         <v>250.2</v>
-      </c>
-      <c r="G129" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="C130" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D130" t="s">
-        <v>30</v>
-      </c>
-      <c r="E130" s="1">
-        <v>1</v>
-      </c>
-      <c r="F130" s="1">
-        <v>250.4</v>
-      </c>
-      <c r="G130" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="C131" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D131" t="s">
-        <v>31</v>
-      </c>
-      <c r="E131" s="1">
-        <v>1</v>
-      </c>
-      <c r="F131" s="1">
-        <v>250.4</v>
       </c>
       <c r="G131" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B132" t="s">
+    <row r="132" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="C132" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D132" t="s">
+        <v>30</v>
+      </c>
+      <c r="E132" s="1">
+        <v>1</v>
+      </c>
+      <c r="F132" s="1">
+        <v>250.4</v>
+      </c>
+      <c r="G132" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="133" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="C133" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D133" t="s">
+        <v>31</v>
+      </c>
+      <c r="E133" s="1">
+        <v>1</v>
+      </c>
+      <c r="F133" s="1">
+        <v>250.4</v>
+      </c>
+      <c r="G133" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="134" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B134" t="s">
         <v>33</v>
       </c>
-      <c r="C132" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D132" s="1" t="s">
+      <c r="C134" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D134" s="1" t="s">
         <v>29</v>
-      </c>
-      <c r="E132" s="1">
-        <v>0</v>
-      </c>
-      <c r="F132" s="1">
-        <v>250.1</v>
-      </c>
-    </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="C133" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D133" t="s">
-        <v>30</v>
-      </c>
-      <c r="E133" s="1">
-        <v>0</v>
-      </c>
-      <c r="F133" s="1">
-        <v>250.2</v>
-      </c>
-    </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="C134" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D134" t="s">
-        <v>31</v>
       </c>
       <c r="E134" s="1">
         <v>0</v>
@@ -2772,95 +3293,98 @@
       <c r="F134" s="1">
         <v>250.1</v>
       </c>
-    </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G134"/>
+    </row>
+    <row r="135" spans="2:11" x14ac:dyDescent="0.2">
       <c r="C135" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D135" s="1" t="s">
+      <c r="D135" t="s">
+        <v>30</v>
+      </c>
+      <c r="E135" s="1">
+        <v>0</v>
+      </c>
+      <c r="F135" s="1">
+        <v>250.2</v>
+      </c>
+      <c r="G135"/>
+    </row>
+    <row r="136" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="C136" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D136" t="s">
+        <v>31</v>
+      </c>
+      <c r="E136" s="1">
+        <v>0</v>
+      </c>
+      <c r="F136" s="1">
+        <v>250.1</v>
+      </c>
+      <c r="G136"/>
+    </row>
+    <row r="137" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="C137" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D137" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E135" s="1">
-        <v>1</v>
-      </c>
-      <c r="F135" s="1">
+      <c r="E137" s="1">
+        <v>1</v>
+      </c>
+      <c r="F137" s="1">
         <v>250.1</v>
-      </c>
-      <c r="G135" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="C136" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D136" t="s">
-        <v>30</v>
-      </c>
-      <c r="E136" s="1">
-        <v>1</v>
-      </c>
-      <c r="F136" s="1">
-        <v>250.2</v>
-      </c>
-      <c r="G136" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="C137" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D137" t="s">
-        <v>31</v>
-      </c>
-      <c r="E137" s="1">
-        <v>1</v>
-      </c>
-      <c r="F137" s="1">
-        <v>250.4</v>
       </c>
       <c r="G137" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B138" t="s">
+    <row r="138" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="C138" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D138" t="s">
+        <v>30</v>
+      </c>
+      <c r="E138" s="1">
+        <v>1</v>
+      </c>
+      <c r="F138" s="1">
+        <v>250.2</v>
+      </c>
+      <c r="G138" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="139" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="C139" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D139" t="s">
+        <v>31</v>
+      </c>
+      <c r="E139" s="1">
+        <v>1</v>
+      </c>
+      <c r="F139" s="1">
+        <v>250.4</v>
+      </c>
+      <c r="G139" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="140" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B140" t="s">
         <v>34</v>
       </c>
-      <c r="C138" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D138" s="1" t="s">
+      <c r="C140" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D140" s="1" t="s">
         <v>29</v>
-      </c>
-      <c r="E138" s="1">
-        <v>0</v>
-      </c>
-      <c r="F138" s="1">
-        <v>1000.1</v>
-      </c>
-    </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="C139" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D139" t="s">
-        <v>30</v>
-      </c>
-      <c r="E139" s="1">
-        <v>0</v>
-      </c>
-      <c r="F139" s="1">
-        <v>1000.2</v>
-      </c>
-    </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="C140" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D140" t="s">
-        <v>31</v>
       </c>
       <c r="E140" s="1">
         <v>0</v>
@@ -2868,47 +3392,44 @@
       <c r="F140" s="1">
         <v>1000.1</v>
       </c>
-    </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G140"/>
+    </row>
+    <row r="141" spans="2:11" x14ac:dyDescent="0.2">
       <c r="C141" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D141" s="1" t="s">
-        <v>29</v>
+      <c r="D141" t="s">
+        <v>30</v>
       </c>
       <c r="E141" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F141" s="1">
         <v>1000.2</v>
       </c>
-      <c r="G141" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G141"/>
+    </row>
+    <row r="142" spans="2:11" x14ac:dyDescent="0.2">
       <c r="C142" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D142" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E142" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F142" s="1">
-        <v>1000.4</v>
-      </c>
-      <c r="G142" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.2">
+        <v>1000.1</v>
+      </c>
+      <c r="G142"/>
+    </row>
+    <row r="143" spans="2:11" x14ac:dyDescent="0.2">
       <c r="C143" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D143" t="s">
-        <v>31</v>
+      <c r="D143" s="1" t="s">
+        <v>29</v>
       </c>
       <c r="E143" s="1">
         <v>1</v>
@@ -2919,208 +3440,232 @@
       <c r="G143" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A144" t="s">
-        <v>35</v>
-      </c>
-      <c r="B144" t="s">
-        <v>36</v>
-      </c>
+      <c r="J143" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="144" spans="2:11" x14ac:dyDescent="0.2">
       <c r="C144" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D144" s="1">
-        <v>1</v>
+      <c r="D144" t="s">
+        <v>30</v>
       </c>
       <c r="E144" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F144" s="1">
-        <v>1000.1</v>
-      </c>
-    </row>
-    <row r="145" spans="2:7" x14ac:dyDescent="0.2">
+        <v>1000.4</v>
+      </c>
+      <c r="G144" t="s">
+        <v>45</v>
+      </c>
+      <c r="J144" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="K144" s="1"/>
+    </row>
+    <row r="145" spans="1:11" x14ac:dyDescent="0.2">
       <c r="C145" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D145">
-        <v>2</v>
+      <c r="D145" t="s">
+        <v>31</v>
       </c>
       <c r="E145" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F145" s="1">
         <v>1000.2</v>
       </c>
-    </row>
-    <row r="146" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="G145" t="s">
+        <v>45</v>
+      </c>
+      <c r="J145" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="K145" s="1"/>
+    </row>
+    <row r="146" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A146" t="s">
+        <v>35</v>
+      </c>
+      <c r="B146" t="s">
+        <v>36</v>
+      </c>
       <c r="C146" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D146">
+      <c r="D146" s="1">
+        <v>1</v>
+      </c>
+      <c r="E146" s="1">
+        <v>0</v>
+      </c>
+      <c r="F146" s="1">
+        <v>1000.1</v>
+      </c>
+      <c r="G146"/>
+      <c r="J146" s="1"/>
+      <c r="K146" s="1"/>
+    </row>
+    <row r="147" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="C147" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D147">
+        <v>2</v>
+      </c>
+      <c r="E147" s="1">
+        <v>0</v>
+      </c>
+      <c r="F147" s="1">
+        <v>1000.2</v>
+      </c>
+      <c r="K147" s="1"/>
+    </row>
+    <row r="148" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="C148" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D148">
         <v>3</v>
       </c>
-      <c r="E146" s="1">
-        <v>0</v>
-      </c>
-      <c r="F146" s="1">
+      <c r="E148" s="1">
+        <v>0</v>
+      </c>
+      <c r="F148" s="1">
         <v>1000.4</v>
       </c>
     </row>
-    <row r="147" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="C147" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D147">
-        <v>4</v>
-      </c>
-      <c r="E147" s="1">
-        <v>0</v>
-      </c>
-      <c r="F147" s="1">
+    <row r="149" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="C149" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D149">
+        <v>4</v>
+      </c>
+      <c r="E149" s="1">
+        <v>0</v>
+      </c>
+      <c r="F149" s="1">
         <v>1000.4</v>
       </c>
     </row>
-    <row r="148" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="C148" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D148">
+    <row r="150" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="C150" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D150">
         <v>5</v>
       </c>
-      <c r="E148" s="1">
-        <v>0</v>
-      </c>
-      <c r="F148" s="1" t="s">
+      <c r="E150" s="1">
+        <v>0</v>
+      </c>
+      <c r="F150" s="1" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="149" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="C149" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D149" s="1">
-        <v>1</v>
-      </c>
-      <c r="E149" s="1">
-        <v>1</v>
-      </c>
-      <c r="F149" s="1">
+    <row r="151" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="C151" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D151" s="1">
+        <v>1</v>
+      </c>
+      <c r="E151" s="1">
+        <v>1</v>
+      </c>
+      <c r="F151" s="1">
         <v>1000.2</v>
       </c>
-      <c r="G149" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="150" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="C150" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D150">
-        <v>2</v>
-      </c>
-      <c r="E150" s="1">
-        <v>1</v>
-      </c>
-      <c r="F150" s="1">
+      <c r="G151" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="152" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="C152" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D152">
+        <v>2</v>
+      </c>
+      <c r="E152" s="1">
+        <v>1</v>
+      </c>
+      <c r="F152" s="1">
         <v>1000.4</v>
       </c>
-      <c r="G150" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="151" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="C151" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D151">
+      <c r="G152" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="I152" s="1"/>
+      <c r="J152" s="1"/>
+      <c r="K152" s="1"/>
+    </row>
+    <row r="153" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="C153" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D153">
         <v>3</v>
       </c>
-      <c r="E151" s="1">
-        <v>1</v>
-      </c>
-      <c r="F151" s="1">
+      <c r="E153" s="1">
+        <v>1</v>
+      </c>
+      <c r="F153" s="1">
         <v>1000.4</v>
       </c>
-      <c r="G151" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="152" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="C152" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D152">
-        <v>4</v>
-      </c>
-      <c r="E152" s="1">
-        <v>1</v>
-      </c>
-      <c r="F152" s="1" t="s">
+      <c r="G153" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="I153" s="1"/>
+      <c r="J153" s="1"/>
+    </row>
+    <row r="154" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="C154" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D154">
+        <v>4</v>
+      </c>
+      <c r="E154" s="1">
+        <v>1</v>
+      </c>
+      <c r="F154" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="G152" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="153" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="C153" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D153">
+      <c r="G154" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="I154" s="1"/>
+      <c r="J154" s="1"/>
+    </row>
+    <row r="155" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="C155" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D155">
         <v>5</v>
       </c>
-      <c r="E153" s="1">
-        <v>1</v>
-      </c>
-      <c r="F153" s="1" t="s">
+      <c r="E155" s="1">
+        <v>1</v>
+      </c>
+      <c r="F155" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="G153" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="154" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="C154" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D154" s="1">
-        <v>1</v>
-      </c>
-      <c r="E154" s="1">
-        <v>2</v>
-      </c>
-      <c r="F154" s="1">
-        <v>1000.4</v>
-      </c>
-      <c r="G154" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="155" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="C155" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D155">
-        <v>2</v>
-      </c>
-      <c r="E155" s="1">
-        <v>2</v>
-      </c>
-      <c r="F155" s="1">
-        <v>1000.4</v>
-      </c>
-      <c r="G155" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="156" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="G155" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="I155" s="1"/>
+      <c r="J155" s="1"/>
+    </row>
+    <row r="156" spans="1:11" x14ac:dyDescent="0.2">
       <c r="C156" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D156">
-        <v>3</v>
+      <c r="D156" s="1">
+        <v>1</v>
       </c>
       <c r="E156" s="1">
         <v>2</v>
@@ -3128,276 +3673,300 @@
       <c r="F156" s="1">
         <v>1000.4</v>
       </c>
-      <c r="G156" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="157" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="G156" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="I156" s="1"/>
+      <c r="J156" s="1"/>
+    </row>
+    <row r="157" spans="1:11" x14ac:dyDescent="0.2">
       <c r="C157" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D157">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E157" s="1">
         <v>2</v>
       </c>
-      <c r="F157" s="1" t="s">
+      <c r="F157" s="1">
+        <v>1000.4</v>
+      </c>
+      <c r="G157" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="I157" s="1"/>
+      <c r="J157" s="1"/>
+    </row>
+    <row r="158" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="C158" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D158">
+        <v>3</v>
+      </c>
+      <c r="E158" s="1">
+        <v>2</v>
+      </c>
+      <c r="F158" s="1">
+        <v>1000.4</v>
+      </c>
+      <c r="G158" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="I158" s="1"/>
+      <c r="J158" s="1"/>
+    </row>
+    <row r="159" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="C159" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D159">
+        <v>4</v>
+      </c>
+      <c r="E159" s="1">
+        <v>2</v>
+      </c>
+      <c r="F159" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="G157" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="158" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="C158" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D158">
+      <c r="G159" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="I159" s="1"/>
+      <c r="J159" s="1"/>
+    </row>
+    <row r="160" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="C160" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D160">
         <v>5</v>
       </c>
-      <c r="E158" s="1">
-        <v>2</v>
-      </c>
-      <c r="F158" s="1" t="s">
+      <c r="E160" s="1">
+        <v>2</v>
+      </c>
+      <c r="F160" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="G158" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="159" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B159" t="s">
+      <c r="G160" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="I160" s="1"/>
+      <c r="J160" s="1"/>
+    </row>
+    <row r="161" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="B161" t="s">
         <v>37</v>
       </c>
-      <c r="C159" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D159" s="1">
-        <v>1</v>
-      </c>
-      <c r="E159" s="1">
-        <v>0</v>
-      </c>
-      <c r="F159" s="1">
+      <c r="C161" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D161" s="1">
+        <v>1</v>
+      </c>
+      <c r="E161" s="1">
+        <v>0</v>
+      </c>
+      <c r="F161" s="1">
         <v>1000.1</v>
       </c>
-    </row>
-    <row r="160" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="C160" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D160">
-        <v>2</v>
-      </c>
-      <c r="E160" s="1">
-        <v>0</v>
-      </c>
-      <c r="F160" s="1">
+      <c r="I161" s="1"/>
+      <c r="J161" s="1"/>
+    </row>
+    <row r="162" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="C162" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D162">
+        <v>2</v>
+      </c>
+      <c r="E162" s="1">
+        <v>0</v>
+      </c>
+      <c r="F162" s="1">
         <v>1000.1</v>
       </c>
     </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="C161" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D161">
+    <row r="163" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="C163" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D163">
         <v>3</v>
       </c>
-      <c r="E161" s="1">
-        <v>0</v>
-      </c>
-      <c r="F161" s="1">
+      <c r="E163" s="1">
+        <v>0</v>
+      </c>
+      <c r="F163" s="1">
         <v>1000.2</v>
       </c>
     </row>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="C162" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D162">
-        <v>4</v>
-      </c>
-      <c r="E162" s="1">
-        <v>0</v>
-      </c>
-      <c r="F162" s="1">
+    <row r="164" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="C164" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D164">
+        <v>4</v>
+      </c>
+      <c r="E164" s="1">
+        <v>0</v>
+      </c>
+      <c r="F164" s="1">
         <v>1000.2</v>
       </c>
     </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="C163" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D163">
+    <row r="165" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="C165" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D165">
         <v>5</v>
       </c>
-      <c r="E163" s="1">
-        <v>0</v>
-      </c>
-      <c r="F163" s="1">
+      <c r="E165" s="1">
+        <v>0</v>
+      </c>
+      <c r="F165" s="1">
         <v>1000.4</v>
       </c>
     </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="C164" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D164" s="1">
-        <v>1</v>
-      </c>
-      <c r="E164" s="1">
-        <v>1</v>
-      </c>
-      <c r="F164" s="1">
+    <row r="166" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="C166" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D166" s="1">
+        <v>1</v>
+      </c>
+      <c r="E166" s="1">
+        <v>1</v>
+      </c>
+      <c r="F166" s="1">
         <v>1000.1</v>
       </c>
-      <c r="G164" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="C165" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D165">
-        <v>2</v>
-      </c>
-      <c r="E165" s="1">
-        <v>1</v>
-      </c>
-      <c r="F165" s="1">
+      <c r="G166" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="167" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="C167" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D167">
+        <v>2</v>
+      </c>
+      <c r="E167" s="1">
+        <v>1</v>
+      </c>
+      <c r="F167" s="1">
         <v>1000.2</v>
       </c>
-      <c r="G165" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="C166" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D166">
+      <c r="G167" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="I167" s="1"/>
+      <c r="J167" s="1"/>
+    </row>
+    <row r="168" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="C168" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D168">
         <v>3</v>
       </c>
-      <c r="E166" s="1">
-        <v>1</v>
-      </c>
-      <c r="F166" s="1">
+      <c r="E168" s="1">
+        <v>1</v>
+      </c>
+      <c r="F168" s="1">
         <v>1000.2</v>
       </c>
-      <c r="G166" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="C167" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D167">
-        <v>4</v>
-      </c>
-      <c r="E167" s="1">
-        <v>1</v>
-      </c>
-      <c r="F167" s="1">
+      <c r="G168" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="I168" s="1"/>
+      <c r="J168" s="1"/>
+    </row>
+    <row r="169" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="C169" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D169">
+        <v>4</v>
+      </c>
+      <c r="E169" s="1">
+        <v>1</v>
+      </c>
+      <c r="F169" s="1">
         <v>1000.4</v>
       </c>
-      <c r="G167" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="C168" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D168">
+      <c r="G169" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="I169" s="1"/>
+      <c r="J169" s="1"/>
+    </row>
+    <row r="170" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="C170" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D170">
         <v>5</v>
       </c>
-      <c r="E168" s="1">
-        <v>1</v>
-      </c>
-      <c r="F168" s="1">
+      <c r="E170" s="1">
+        <v>1</v>
+      </c>
+      <c r="F170" s="1">
         <v>1000.4</v>
       </c>
-      <c r="G168" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="C169" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D169" s="1">
-        <v>1</v>
-      </c>
-      <c r="E169" s="1">
-        <v>2</v>
-      </c>
-      <c r="F169" s="1">
+      <c r="G170" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="I170" s="1"/>
+      <c r="J170" s="1"/>
+    </row>
+    <row r="171" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="C171" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D171" s="1">
+        <v>1</v>
+      </c>
+      <c r="E171" s="1">
+        <v>2</v>
+      </c>
+      <c r="F171" s="1">
         <v>1000.2</v>
       </c>
-      <c r="G169" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="C170" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D170">
-        <v>2</v>
-      </c>
-      <c r="E170" s="1">
-        <v>2</v>
-      </c>
-      <c r="F170" s="1">
+      <c r="G171" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="I171" s="1"/>
+      <c r="J171" s="1"/>
+    </row>
+    <row r="172" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="C172" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D172">
+        <v>2</v>
+      </c>
+      <c r="E172" s="1">
+        <v>2</v>
+      </c>
+      <c r="F172" s="1">
         <v>1000.2</v>
       </c>
-      <c r="G170" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="C171" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D171">
+      <c r="G172" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="I172" s="1"/>
+      <c r="J172" s="1"/>
+    </row>
+    <row r="173" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="C173" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D173">
         <v>3</v>
-      </c>
-      <c r="E171" s="1">
-        <v>2</v>
-      </c>
-      <c r="F171" s="1">
-        <v>1000.4</v>
-      </c>
-      <c r="G171" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="C172" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D172">
-        <v>4</v>
-      </c>
-      <c r="E172" s="1">
-        <v>2</v>
-      </c>
-      <c r="F172" s="1">
-        <v>1000.4</v>
-      </c>
-      <c r="G172" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="C173" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D173">
-        <v>5</v>
       </c>
       <c r="E173" s="1">
         <v>2</v>
@@ -3405,127 +3974,156 @@
       <c r="F173" s="1">
         <v>1000.4</v>
       </c>
-      <c r="G173" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A174" t="s">
-        <v>47</v>
-      </c>
-      <c r="B174" t="s">
+      <c r="G173" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="I173" s="1"/>
+      <c r="J173" s="1"/>
+    </row>
+    <row r="174" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="C174" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D174">
+        <v>4</v>
+      </c>
+      <c r="E174" s="1">
+        <v>2</v>
+      </c>
+      <c r="F174" s="1">
+        <v>1000.4</v>
+      </c>
+      <c r="G174" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="I174" s="1"/>
+      <c r="J174" s="1"/>
+    </row>
+    <row r="175" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="C175" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D175">
+        <v>5</v>
+      </c>
+      <c r="E175" s="1">
+        <v>2</v>
+      </c>
+      <c r="F175" s="1">
+        <v>1000.4</v>
+      </c>
+      <c r="G175" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="I175" s="1"/>
+      <c r="J175" s="1"/>
+    </row>
+    <row r="176" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A176" t="s">
+        <v>41</v>
+      </c>
+      <c r="B176" t="s">
         <v>48</v>
       </c>
-      <c r="C174" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D174">
-        <v>2</v>
-      </c>
-      <c r="E174" s="1">
-        <v>0</v>
-      </c>
-      <c r="F174" s="1">
+      <c r="C176" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D176">
+        <v>2</v>
+      </c>
+      <c r="E176" s="1">
+        <v>0</v>
+      </c>
+      <c r="F176" s="1">
         <v>125.1</v>
       </c>
-    </row>
-    <row r="175" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="C175" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D175">
-        <v>2</v>
-      </c>
-      <c r="E175" s="1">
-        <v>1</v>
-      </c>
-      <c r="F175" s="1">
+      <c r="I176" s="1"/>
+      <c r="J176" s="1"/>
+    </row>
+    <row r="177" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="C177" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D177">
+        <v>2</v>
+      </c>
+      <c r="E177" s="1">
+        <v>1</v>
+      </c>
+      <c r="F177" s="1">
         <v>250.2</v>
       </c>
-      <c r="G175" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="176" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="C176" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D176">
-        <v>4</v>
-      </c>
-      <c r="E176" s="1">
-        <v>0</v>
-      </c>
-      <c r="F176" s="1">
+      <c r="G177" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H177" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="I177" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="178" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="C178" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D178">
+        <v>4</v>
+      </c>
+      <c r="E178" s="1">
+        <v>0</v>
+      </c>
+      <c r="F178" s="1">
         <v>125.2</v>
       </c>
     </row>
-    <row r="177" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="C177" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D177">
-        <v>4</v>
-      </c>
-      <c r="E177" s="1">
-        <v>1</v>
-      </c>
-      <c r="F177" s="1">
-        <v>250.4</v>
-      </c>
-      <c r="G177" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="178" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="C178" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D178">
-        <v>4</v>
-      </c>
-      <c r="E178" s="1">
-        <v>2</v>
-      </c>
-      <c r="F178" s="1">
-        <v>250.4</v>
-      </c>
-      <c r="G178" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="179" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="179" spans="2:9" x14ac:dyDescent="0.2">
       <c r="C179" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D179">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E179" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F179" s="1">
         <v>250.4</v>
       </c>
-    </row>
-    <row r="180" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="G179" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H179" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="I179" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="180" spans="2:9" x14ac:dyDescent="0.2">
       <c r="C180" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D180">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E180" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F180" s="1">
         <v>250.4</v>
       </c>
-      <c r="G180" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="181" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="G180" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H180" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="I180" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="181" spans="2:9" x14ac:dyDescent="0.2">
       <c r="C181" s="1" t="s">
         <v>21</v>
       </c>
@@ -3533,47 +4131,59 @@
         <v>6</v>
       </c>
       <c r="E181" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F181" s="1">
         <v>250.4</v>
       </c>
-      <c r="G181" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="182" spans="2:7" x14ac:dyDescent="0.2">
+    </row>
+    <row r="182" spans="2:9" x14ac:dyDescent="0.2">
       <c r="C182" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D182">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E182" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F182" s="1">
         <v>250.4</v>
       </c>
-    </row>
-    <row r="183" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="G182" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H182" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="I182" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="183" spans="2:9" x14ac:dyDescent="0.2">
       <c r="C183" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D183">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E183" s="1">
-        <v>1</v>
-      </c>
-      <c r="F183" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="G183" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="184" spans="2:7" x14ac:dyDescent="0.2">
+        <v>2</v>
+      </c>
+      <c r="F183" s="1">
+        <v>250.4</v>
+      </c>
+      <c r="G183" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H183" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="I183" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="184" spans="2:9" x14ac:dyDescent="0.2">
       <c r="C184" s="1" t="s">
         <v>21</v>
       </c>
@@ -3581,129 +4191,159 @@
         <v>8</v>
       </c>
       <c r="E184" s="1">
-        <v>2</v>
-      </c>
-      <c r="F184" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="F184" s="1">
+        <v>250.4</v>
+      </c>
+    </row>
+    <row r="185" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="C185" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D185">
+        <v>8</v>
+      </c>
+      <c r="E185" s="1">
+        <v>1</v>
+      </c>
+      <c r="F185" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G185" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H185" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="I185" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="186" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="C186" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D186">
+        <v>8</v>
+      </c>
+      <c r="E186" s="1">
+        <v>2</v>
+      </c>
+      <c r="F186" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="G184" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="185" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B185" t="s">
+      <c r="G186" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H186" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="I186" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="187" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B187" t="s">
         <v>49</v>
       </c>
-      <c r="C185" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D185">
-        <v>2</v>
-      </c>
-      <c r="E185" s="1">
-        <v>0</v>
-      </c>
-      <c r="F185" s="1">
+      <c r="C187" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D187">
+        <v>2</v>
+      </c>
+      <c r="E187" s="1">
+        <v>0</v>
+      </c>
+      <c r="F187" s="1">
         <v>250.1</v>
       </c>
     </row>
-    <row r="186" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="C186" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D186">
-        <v>2</v>
-      </c>
-      <c r="E186" s="1">
-        <v>1</v>
-      </c>
-      <c r="F186" s="1">
+    <row r="188" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="C188" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D188">
+        <v>2</v>
+      </c>
+      <c r="E188" s="1">
+        <v>1</v>
+      </c>
+      <c r="F188" s="1">
         <v>250.2</v>
       </c>
-      <c r="G186" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="187" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="C187" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D187">
-        <v>4</v>
-      </c>
-      <c r="E187" s="1">
-        <v>0</v>
-      </c>
-      <c r="F187" s="1">
+      <c r="G188" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H188" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="I188" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="189" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="C189" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D189">
+        <v>4</v>
+      </c>
+      <c r="E189" s="1">
+        <v>0</v>
+      </c>
+      <c r="F189" s="1">
         <v>250.2</v>
       </c>
     </row>
-    <row r="188" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="C188" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D188">
-        <v>4</v>
-      </c>
-      <c r="E188" s="1">
-        <v>1</v>
-      </c>
-      <c r="F188" s="1">
-        <v>250.4</v>
-      </c>
-      <c r="G188" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="189" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="C189" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D189">
-        <v>4</v>
-      </c>
-      <c r="E189" s="1">
-        <v>2</v>
-      </c>
-      <c r="F189" s="1">
-        <v>250.4</v>
-      </c>
-      <c r="G189" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="190" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="190" spans="2:9" x14ac:dyDescent="0.2">
       <c r="C190" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D190">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E190" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F190" s="1">
         <v>250.4</v>
       </c>
-    </row>
-    <row r="191" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="G190" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H190" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="I190" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="191" spans="2:9" x14ac:dyDescent="0.2">
       <c r="C191" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D191">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E191" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F191" s="1">
         <v>250.4</v>
       </c>
-      <c r="G191" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="192" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="G191" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H191" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="I191" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="192" spans="2:9" x14ac:dyDescent="0.2">
       <c r="C192" s="1" t="s">
         <v>21</v>
       </c>
@@ -3711,47 +4351,59 @@
         <v>6</v>
       </c>
       <c r="E192" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F192" s="1">
         <v>250.4</v>
       </c>
-      <c r="G192" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="193" spans="2:7" x14ac:dyDescent="0.2">
+    </row>
+    <row r="193" spans="2:9" x14ac:dyDescent="0.2">
       <c r="C193" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D193">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E193" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F193" s="1">
         <v>250.4</v>
       </c>
-    </row>
-    <row r="194" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="G193" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H193" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="I193" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="194" spans="2:9" x14ac:dyDescent="0.2">
       <c r="C194" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D194">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E194" s="1">
-        <v>1</v>
-      </c>
-      <c r="F194" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G194" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="195" spans="2:7" x14ac:dyDescent="0.2">
+        <v>2</v>
+      </c>
+      <c r="F194" s="1">
+        <v>250.4</v>
+      </c>
+      <c r="G194" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H194" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="I194" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="195" spans="2:9" x14ac:dyDescent="0.2">
       <c r="C195" s="1" t="s">
         <v>21</v>
       </c>
@@ -3759,129 +4411,159 @@
         <v>8</v>
       </c>
       <c r="E195" s="1">
-        <v>2</v>
-      </c>
-      <c r="F195" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="F195" s="1">
+        <v>250.4</v>
+      </c>
+    </row>
+    <row r="196" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="C196" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D196">
+        <v>8</v>
+      </c>
+      <c r="E196" s="1">
+        <v>1</v>
+      </c>
+      <c r="F196" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G196" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H196" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="I196" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="197" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="C197" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D197">
+        <v>8</v>
+      </c>
+      <c r="E197" s="1">
+        <v>2</v>
+      </c>
+      <c r="F197" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G195" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="196" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B196" t="s">
+      <c r="G197" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H197" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="I197" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="198" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B198" t="s">
         <v>50</v>
       </c>
-      <c r="C196" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D196">
-        <v>2</v>
-      </c>
-      <c r="E196" s="1">
-        <v>0</v>
-      </c>
-      <c r="F196" s="1">
+      <c r="C198" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D198">
+        <v>2</v>
+      </c>
+      <c r="E198" s="1">
+        <v>0</v>
+      </c>
+      <c r="F198" s="1">
         <v>250.1</v>
       </c>
     </row>
-    <row r="197" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="C197" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D197">
-        <v>2</v>
-      </c>
-      <c r="E197" s="1">
-        <v>1</v>
-      </c>
-      <c r="F197" s="1">
+    <row r="199" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="C199" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D199">
+        <v>2</v>
+      </c>
+      <c r="E199" s="1">
+        <v>1</v>
+      </c>
+      <c r="F199" s="1">
         <v>250.2</v>
       </c>
-      <c r="G197" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="198" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="C198" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D198">
-        <v>4</v>
-      </c>
-      <c r="E198" s="1">
-        <v>0</v>
-      </c>
-      <c r="F198" s="1">
+      <c r="G199" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H199" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="I199" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="200" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="C200" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D200">
+        <v>4</v>
+      </c>
+      <c r="E200" s="1">
+        <v>0</v>
+      </c>
+      <c r="F200" s="1">
         <v>250.2</v>
       </c>
     </row>
-    <row r="199" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="C199" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D199">
-        <v>4</v>
-      </c>
-      <c r="E199" s="1">
-        <v>1</v>
-      </c>
-      <c r="F199" s="1">
-        <v>250.4</v>
-      </c>
-      <c r="G199" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="200" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="C200" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D200">
-        <v>4</v>
-      </c>
-      <c r="E200" s="1">
-        <v>2</v>
-      </c>
-      <c r="F200" s="1">
-        <v>250.4</v>
-      </c>
-      <c r="G200" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="201" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="201" spans="2:9" x14ac:dyDescent="0.2">
       <c r="C201" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D201">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E201" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F201" s="1">
         <v>250.4</v>
       </c>
-    </row>
-    <row r="202" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="G201" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H201" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="I201" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="202" spans="2:9" x14ac:dyDescent="0.2">
       <c r="C202" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D202">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E202" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F202" s="1">
         <v>250.4</v>
       </c>
-      <c r="G202" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="203" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="G202" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H202" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="I202" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="203" spans="2:9" x14ac:dyDescent="0.2">
       <c r="C203" s="1" t="s">
         <v>21</v>
       </c>
@@ -3889,47 +4571,59 @@
         <v>6</v>
       </c>
       <c r="E203" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F203" s="1">
         <v>250.4</v>
       </c>
-      <c r="G203" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="204" spans="2:7" x14ac:dyDescent="0.2">
+    </row>
+    <row r="204" spans="2:9" x14ac:dyDescent="0.2">
       <c r="C204" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D204">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E204" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F204" s="1">
         <v>250.4</v>
       </c>
-    </row>
-    <row r="205" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="G204" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H204" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="I204" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="205" spans="2:9" x14ac:dyDescent="0.2">
       <c r="C205" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D205">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E205" s="1">
-        <v>1</v>
-      </c>
-      <c r="F205" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G205" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="206" spans="2:7" x14ac:dyDescent="0.2">
+        <v>2</v>
+      </c>
+      <c r="F205" s="1">
+        <v>250.4</v>
+      </c>
+      <c r="G205" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H205" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="I205" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="206" spans="2:9" x14ac:dyDescent="0.2">
       <c r="C206" s="1" t="s">
         <v>21</v>
       </c>
@@ -3937,129 +4631,159 @@
         <v>8</v>
       </c>
       <c r="E206" s="1">
-        <v>2</v>
-      </c>
-      <c r="F206" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="F206" s="1">
+        <v>250.4</v>
+      </c>
+    </row>
+    <row r="207" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="C207" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D207">
+        <v>8</v>
+      </c>
+      <c r="E207" s="1">
+        <v>1</v>
+      </c>
+      <c r="F207" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G207" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H207" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="I207" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="208" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="C208" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D208">
+        <v>8</v>
+      </c>
+      <c r="E208" s="1">
+        <v>2</v>
+      </c>
+      <c r="F208" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G206" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="207" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B207" t="s">
+      <c r="G208" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H208" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="I208" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="209" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B209" t="s">
         <v>51</v>
       </c>
-      <c r="C207" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D207">
-        <v>2</v>
-      </c>
-      <c r="E207" s="1">
-        <v>0</v>
-      </c>
-      <c r="F207" s="1">
+      <c r="C209" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D209">
+        <v>2</v>
+      </c>
+      <c r="E209" s="1">
+        <v>0</v>
+      </c>
+      <c r="F209" s="1">
         <v>250.1</v>
       </c>
     </row>
-    <row r="208" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="C208" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D208">
-        <v>2</v>
-      </c>
-      <c r="E208" s="1">
-        <v>1</v>
-      </c>
-      <c r="F208" s="1">
+    <row r="210" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="C210" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D210">
+        <v>2</v>
+      </c>
+      <c r="E210" s="1">
+        <v>1</v>
+      </c>
+      <c r="F210" s="1">
         <v>250.2</v>
       </c>
-      <c r="G208" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="209" spans="3:7" x14ac:dyDescent="0.2">
-      <c r="C209" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D209">
-        <v>4</v>
-      </c>
-      <c r="E209" s="1">
-        <v>0</v>
-      </c>
-      <c r="F209" s="1">
+      <c r="G210" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H210" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="I210" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="211" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="C211" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D211">
+        <v>4</v>
+      </c>
+      <c r="E211" s="1">
+        <v>0</v>
+      </c>
+      <c r="F211" s="1">
         <v>250.2</v>
       </c>
     </row>
-    <row r="210" spans="3:7" x14ac:dyDescent="0.2">
-      <c r="C210" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D210">
-        <v>4</v>
-      </c>
-      <c r="E210" s="1">
-        <v>1</v>
-      </c>
-      <c r="F210" s="1">
-        <v>250.4</v>
-      </c>
-      <c r="G210" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="211" spans="3:7" x14ac:dyDescent="0.2">
-      <c r="C211" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D211">
-        <v>4</v>
-      </c>
-      <c r="E211" s="1">
-        <v>2</v>
-      </c>
-      <c r="F211" s="1">
-        <v>250.4</v>
-      </c>
-      <c r="G211" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="212" spans="3:7" x14ac:dyDescent="0.2">
+    <row r="212" spans="2:9" x14ac:dyDescent="0.2">
       <c r="C212" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D212">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E212" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F212" s="1">
         <v>250.4</v>
       </c>
-    </row>
-    <row r="213" spans="3:7" x14ac:dyDescent="0.2">
+      <c r="G212" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H212" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="I212" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="213" spans="2:9" x14ac:dyDescent="0.2">
       <c r="C213" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D213">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E213" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F213" s="1">
         <v>250.4</v>
       </c>
-      <c r="G213" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="214" spans="3:7" x14ac:dyDescent="0.2">
+      <c r="G213" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H213" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="I213" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="214" spans="2:9" x14ac:dyDescent="0.2">
       <c r="C214" s="1" t="s">
         <v>21</v>
       </c>
@@ -4067,47 +4791,59 @@
         <v>6</v>
       </c>
       <c r="E214" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F214" s="1">
         <v>250.4</v>
       </c>
-      <c r="G214" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="215" spans="3:7" x14ac:dyDescent="0.2">
+    </row>
+    <row r="215" spans="2:9" x14ac:dyDescent="0.2">
       <c r="C215" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D215">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E215" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F215" s="1">
         <v>250.4</v>
       </c>
-    </row>
-    <row r="216" spans="3:7" x14ac:dyDescent="0.2">
+      <c r="G215" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H215" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="I215" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="216" spans="2:9" x14ac:dyDescent="0.2">
       <c r="C216" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D216">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E216" s="1">
-        <v>1</v>
-      </c>
-      <c r="F216" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G216" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="217" spans="3:7" x14ac:dyDescent="0.2">
+        <v>2</v>
+      </c>
+      <c r="F216" s="1">
+        <v>250.4</v>
+      </c>
+      <c r="G216" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H216" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="I216" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="217" spans="2:9" x14ac:dyDescent="0.2">
       <c r="C217" s="1" t="s">
         <v>21</v>
       </c>
@@ -4115,16 +4851,62 @@
         <v>8</v>
       </c>
       <c r="E217" s="1">
-        <v>2</v>
-      </c>
-      <c r="F217" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="F217" s="1">
+        <v>250.4</v>
+      </c>
+    </row>
+    <row r="218" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="C218" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D218">
+        <v>8</v>
+      </c>
+      <c r="E218" s="1">
+        <v>1</v>
+      </c>
+      <c r="F218" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G218" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H218" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="I218" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="219" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="C219" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D219">
+        <v>8</v>
+      </c>
+      <c r="E219" s="1">
+        <v>2</v>
+      </c>
+      <c r="F219" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G217" t="s">
-        <v>52</v>
+      <c r="G219" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H219" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="I219" t="s">
+        <v>62</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="I1:K1"/>
+  </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/assests/AmpTest claud4.xlsx
+++ b/assests/AmpTest claud4.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/toddanderson/Documents/claude projects/amplifinder/assests/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1143CEE-83BF-FB4D-819E-B2F63B70EBB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C55C39E4-6EFF-934F-968E-A9EA534DC8EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="740" yWindow="660" windowWidth="27640" windowHeight="16760" xr2:uid="{A2AA72AD-F933-604F-82A4-82C55EAB3989}"/>
   </bookViews>
@@ -167,9 +167,6 @@
     <t xml:space="preserve">Performance </t>
   </si>
   <si>
-    <t xml:space="preserve">Coverage </t>
-  </si>
-  <si>
     <t xml:space="preserve">MOS SUB </t>
   </si>
   <si>
@@ -197,9 +194,6 @@
     <t>AMD210</t>
   </si>
   <si>
-    <t>Coverage</t>
-  </si>
-  <si>
     <t>10HDR</t>
   </si>
   <si>
@@ -225,6 +219,12 @@
   </si>
   <si>
     <t>DSUB6F5K</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enhancement </t>
+  </si>
+  <si>
+    <t>Enhancement</t>
   </si>
 </sst>
 </file>
@@ -689,13 +689,13 @@
         <v>250.1</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>42</v>
@@ -721,10 +721,10 @@
         <v>250.2</v>
       </c>
       <c r="G3" t="s">
+        <v>43</v>
+      </c>
+      <c r="J3" t="s">
         <v>44</v>
-      </c>
-      <c r="J3" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.2">
@@ -760,10 +760,10 @@
         <v>250.4</v>
       </c>
       <c r="G5" t="s">
+        <v>43</v>
+      </c>
+      <c r="J5" t="s">
         <v>44</v>
-      </c>
-      <c r="J5" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.2">
@@ -782,10 +782,10 @@
         <v>250.4</v>
       </c>
       <c r="G6" t="s">
+        <v>43</v>
+      </c>
+      <c r="J6" t="s">
         <v>44</v>
-      </c>
-      <c r="J6" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.2">
@@ -821,10 +821,10 @@
         <v>250.4</v>
       </c>
       <c r="G8" t="s">
+        <v>43</v>
+      </c>
+      <c r="J8" t="s">
         <v>44</v>
-      </c>
-      <c r="J8" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.2">
@@ -843,10 +843,10 @@
         <v>250.4</v>
       </c>
       <c r="G9" t="s">
+        <v>43</v>
+      </c>
+      <c r="J9" t="s">
         <v>44</v>
-      </c>
-      <c r="J9" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.2">
@@ -880,10 +880,10 @@
         <v>8</v>
       </c>
       <c r="G11" t="s">
+        <v>43</v>
+      </c>
+      <c r="J11" t="s">
         <v>44</v>
-      </c>
-      <c r="J11" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.2">
@@ -900,10 +900,10 @@
         <v>9</v>
       </c>
       <c r="G12" t="s">
+        <v>43</v>
+      </c>
+      <c r="J12" t="s">
         <v>44</v>
-      </c>
-      <c r="J12" t="s">
-        <v>45</v>
       </c>
       <c r="M12" s="1"/>
       <c r="N12" s="1"/>
@@ -941,10 +941,10 @@
         <v>250.2</v>
       </c>
       <c r="G14" t="s">
+        <v>45</v>
+      </c>
+      <c r="J14" t="s">
         <v>46</v>
-      </c>
-      <c r="J14" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.2">
@@ -976,10 +976,10 @@
         <v>250.4</v>
       </c>
       <c r="G16" t="s">
+        <v>45</v>
+      </c>
+      <c r="J16" t="s">
         <v>46</v>
-      </c>
-      <c r="J16" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="17" spans="2:12" x14ac:dyDescent="0.2">
@@ -996,10 +996,10 @@
         <v>250.4</v>
       </c>
       <c r="G17" t="s">
+        <v>45</v>
+      </c>
+      <c r="J17" t="s">
         <v>46</v>
-      </c>
-      <c r="J17" t="s">
-        <v>47</v>
       </c>
       <c r="L17" s="1"/>
     </row>
@@ -1032,10 +1032,10 @@
         <v>250.4</v>
       </c>
       <c r="G19" t="s">
+        <v>45</v>
+      </c>
+      <c r="J19" t="s">
         <v>46</v>
-      </c>
-      <c r="J19" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="20" spans="2:12" x14ac:dyDescent="0.2">
@@ -1052,10 +1052,10 @@
         <v>250.4</v>
       </c>
       <c r="G20" t="s">
+        <v>45</v>
+      </c>
+      <c r="J20" t="s">
         <v>46</v>
-      </c>
-      <c r="J20" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="21" spans="2:12" x14ac:dyDescent="0.2">
@@ -1087,10 +1087,10 @@
         <v>11</v>
       </c>
       <c r="G22" t="s">
+        <v>45</v>
+      </c>
+      <c r="J22" t="s">
         <v>46</v>
-      </c>
-      <c r="J22" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="23" spans="2:12" x14ac:dyDescent="0.2">
@@ -1107,10 +1107,10 @@
         <v>12</v>
       </c>
       <c r="G23" t="s">
+        <v>45</v>
+      </c>
+      <c r="J23" t="s">
         <v>46</v>
-      </c>
-      <c r="J23" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="24" spans="2:12" x14ac:dyDescent="0.2">
@@ -1146,10 +1146,10 @@
         <v>250.2</v>
       </c>
       <c r="G25" t="s">
+        <v>45</v>
+      </c>
+      <c r="J25" t="s">
         <v>46</v>
-      </c>
-      <c r="J25" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.2">
@@ -1181,10 +1181,10 @@
         <v>250.4</v>
       </c>
       <c r="G27" t="s">
+        <v>45</v>
+      </c>
+      <c r="J27" t="s">
         <v>46</v>
-      </c>
-      <c r="J27" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="28" spans="2:12" x14ac:dyDescent="0.2">
@@ -1201,10 +1201,10 @@
         <v>250.4</v>
       </c>
       <c r="G28" t="s">
+        <v>45</v>
+      </c>
+      <c r="J28" t="s">
         <v>46</v>
-      </c>
-      <c r="J28" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="29" spans="2:12" x14ac:dyDescent="0.2">
@@ -1236,10 +1236,10 @@
         <v>250.4</v>
       </c>
       <c r="G30" t="s">
+        <v>45</v>
+      </c>
+      <c r="J30" t="s">
         <v>46</v>
-      </c>
-      <c r="J30" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="31" spans="2:12" x14ac:dyDescent="0.2">
@@ -1256,10 +1256,10 @@
         <v>250.4</v>
       </c>
       <c r="G31" t="s">
+        <v>45</v>
+      </c>
+      <c r="J31" t="s">
         <v>46</v>
-      </c>
-      <c r="J31" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="32" spans="2:12" x14ac:dyDescent="0.2">
@@ -1291,10 +1291,10 @@
         <v>8</v>
       </c>
       <c r="G33" t="s">
+        <v>45</v>
+      </c>
+      <c r="J33" t="s">
         <v>46</v>
-      </c>
-      <c r="J33" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.2">
@@ -1311,10 +1311,10 @@
         <v>9</v>
       </c>
       <c r="G34" t="s">
+        <v>45</v>
+      </c>
+      <c r="J34" t="s">
         <v>46</v>
-      </c>
-      <c r="J34" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.2">
@@ -1350,10 +1350,10 @@
         <v>250.2</v>
       </c>
       <c r="G36" t="s">
+        <v>45</v>
+      </c>
+      <c r="J36" t="s">
         <v>46</v>
-      </c>
-      <c r="J36" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.2">
@@ -1386,10 +1386,10 @@
         <v>250.4</v>
       </c>
       <c r="G38" t="s">
+        <v>45</v>
+      </c>
+      <c r="J38" t="s">
         <v>46</v>
-      </c>
-      <c r="J38" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.2">
@@ -1406,10 +1406,10 @@
         <v>250.4</v>
       </c>
       <c r="G39" t="s">
+        <v>45</v>
+      </c>
+      <c r="J39" t="s">
         <v>46</v>
-      </c>
-      <c r="J39" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.2">
@@ -1442,10 +1442,10 @@
         <v>250.4</v>
       </c>
       <c r="G41" t="s">
+        <v>45</v>
+      </c>
+      <c r="J41" t="s">
         <v>46</v>
-      </c>
-      <c r="J41" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.2">
@@ -1462,10 +1462,10 @@
         <v>250.4</v>
       </c>
       <c r="G42" t="s">
+        <v>45</v>
+      </c>
+      <c r="J42" t="s">
         <v>46</v>
-      </c>
-      <c r="J42" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.2">
@@ -1498,10 +1498,10 @@
         <v>8</v>
       </c>
       <c r="G44" t="s">
+        <v>45</v>
+      </c>
+      <c r="J44" t="s">
         <v>46</v>
-      </c>
-      <c r="J44" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.2">
@@ -1518,10 +1518,10 @@
         <v>9</v>
       </c>
       <c r="G45" t="s">
+        <v>45</v>
+      </c>
+      <c r="J45" t="s">
         <v>46</v>
-      </c>
-      <c r="J45" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.2">
@@ -1573,19 +1573,19 @@
         <v>250.1</v>
       </c>
       <c r="G48" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="H48" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="I48" t="s">
         <v>54</v>
       </c>
-      <c r="H48" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="I48" t="s">
+      <c r="J48" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="K48" t="s">
         <v>56</v>
-      </c>
-      <c r="J48" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="K48" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="49" spans="2:11" x14ac:dyDescent="0.2">
@@ -1602,16 +1602,16 @@
         <v>1000.2</v>
       </c>
       <c r="G49" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="I49" t="s">
         <v>54</v>
       </c>
-      <c r="I49" t="s">
+      <c r="J49" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="K49" t="s">
         <v>56</v>
-      </c>
-      <c r="J49" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="K49" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="50" spans="2:11" x14ac:dyDescent="0.2">
@@ -1656,19 +1656,19 @@
         <v>1000.4</v>
       </c>
       <c r="G52" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="H52" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="I52" t="s">
         <v>54</v>
       </c>
-      <c r="H52" s="1" t="s">
+      <c r="J52" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="I52" t="s">
+      <c r="K52" t="s">
         <v>56</v>
-      </c>
-      <c r="J52" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="K52" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="53" spans="2:11" x14ac:dyDescent="0.2">
@@ -1685,19 +1685,19 @@
         <v>1000.4</v>
       </c>
       <c r="G53" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="H53" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="I53" t="s">
         <v>54</v>
       </c>
-      <c r="H53" s="1" t="s">
+      <c r="J53" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="I53" t="s">
+      <c r="K53" t="s">
         <v>56</v>
-      </c>
-      <c r="J53" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="K53" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="54" spans="2:11" x14ac:dyDescent="0.2">
@@ -1714,19 +1714,19 @@
         <v>1000.4</v>
       </c>
       <c r="G54" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="H54" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="I54" t="s">
         <v>54</v>
       </c>
-      <c r="H54" s="1" t="s">
+      <c r="J54" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="I54" t="s">
+      <c r="K54" t="s">
         <v>56</v>
-      </c>
-      <c r="J54" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="K54" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="55" spans="2:11" x14ac:dyDescent="0.2">
@@ -1743,19 +1743,19 @@
         <v>1000.4</v>
       </c>
       <c r="G55" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="H55" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="I55" t="s">
         <v>54</v>
       </c>
-      <c r="H55" s="1" t="s">
+      <c r="J55" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="I55" t="s">
+      <c r="K55" t="s">
         <v>56</v>
-      </c>
-      <c r="J55" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="K55" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="56" spans="2:11" x14ac:dyDescent="0.2">
@@ -1803,19 +1803,19 @@
         <v>250.1</v>
       </c>
       <c r="G58" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="H58" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="I58" t="s">
         <v>54</v>
       </c>
-      <c r="H58" s="1" t="s">
+      <c r="J58" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="I58" t="s">
+      <c r="K58" t="s">
         <v>56</v>
-      </c>
-      <c r="J58" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="K58" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="59" spans="2:11" x14ac:dyDescent="0.2">
@@ -1832,19 +1832,19 @@
         <v>1000.2</v>
       </c>
       <c r="G59" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="H59" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="I59" t="s">
         <v>54</v>
       </c>
-      <c r="H59" s="1" t="s">
+      <c r="J59" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="I59" t="s">
+      <c r="K59" t="s">
         <v>56</v>
-      </c>
-      <c r="J59" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="K59" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="60" spans="2:11" x14ac:dyDescent="0.2">
@@ -1872,7 +1872,7 @@
         <v>0</v>
       </c>
       <c r="F61" s="1">
-        <v>1000.2</v>
+        <v>250.2</v>
       </c>
     </row>
     <row r="62" spans="2:11" x14ac:dyDescent="0.2">
@@ -1889,19 +1889,19 @@
         <v>1000.4</v>
       </c>
       <c r="G62" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="H62" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="I62" t="s">
         <v>54</v>
       </c>
-      <c r="H62" s="1" t="s">
+      <c r="J62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="I62" t="s">
+      <c r="K62" t="s">
         <v>56</v>
-      </c>
-      <c r="J62" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="K62" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="63" spans="2:11" x14ac:dyDescent="0.2">
@@ -1918,19 +1918,19 @@
         <v>1000.4</v>
       </c>
       <c r="G63" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="H63" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="I63" t="s">
         <v>54</v>
       </c>
-      <c r="H63" s="1" t="s">
+      <c r="J63" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="I63" t="s">
+      <c r="K63" t="s">
         <v>56</v>
-      </c>
-      <c r="J63" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="K63" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="64" spans="2:11" x14ac:dyDescent="0.2">
@@ -1947,19 +1947,19 @@
         <v>1000.4</v>
       </c>
       <c r="G64" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="H64" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="I64" t="s">
         <v>54</v>
       </c>
-      <c r="H64" s="1" t="s">
+      <c r="J64" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="I64" t="s">
+      <c r="K64" t="s">
         <v>56</v>
-      </c>
-      <c r="J64" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="K64" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="65" spans="2:11" x14ac:dyDescent="0.2">
@@ -1976,19 +1976,19 @@
         <v>1000.4</v>
       </c>
       <c r="G65" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="H65" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="I65" t="s">
         <v>54</v>
       </c>
-      <c r="H65" s="1" t="s">
+      <c r="J65" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="I65" t="s">
+      <c r="K65" t="s">
         <v>56</v>
-      </c>
-      <c r="J65" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="K65" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="66" spans="2:11" x14ac:dyDescent="0.2">
@@ -2036,19 +2036,19 @@
         <v>250.1</v>
       </c>
       <c r="G68" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="H68" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="I68" t="s">
         <v>54</v>
       </c>
-      <c r="H68" s="1" t="s">
+      <c r="J68" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="I68" t="s">
+      <c r="K68" t="s">
         <v>56</v>
-      </c>
-      <c r="J68" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="K68" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="69" spans="2:11" x14ac:dyDescent="0.2">
@@ -2065,19 +2065,19 @@
         <v>1000.2</v>
       </c>
       <c r="G69" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="H69" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="I69" t="s">
         <v>54</v>
       </c>
-      <c r="H69" s="1" t="s">
+      <c r="J69" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="I69" t="s">
+      <c r="K69" t="s">
         <v>56</v>
-      </c>
-      <c r="J69" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="K69" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="70" spans="2:11" x14ac:dyDescent="0.2">
@@ -2122,19 +2122,19 @@
         <v>1000.4</v>
       </c>
       <c r="G72" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="H72" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="I72" t="s">
         <v>54</v>
       </c>
-      <c r="H72" s="1" t="s">
+      <c r="J72" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="I72" t="s">
+      <c r="K72" t="s">
         <v>56</v>
-      </c>
-      <c r="J72" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="K72" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="73" spans="2:11" x14ac:dyDescent="0.2">
@@ -2151,19 +2151,19 @@
         <v>1000.4</v>
       </c>
       <c r="G73" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="H73" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="I73" t="s">
         <v>54</v>
       </c>
-      <c r="H73" s="1" t="s">
+      <c r="J73" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="I73" t="s">
+      <c r="K73" t="s">
         <v>56</v>
-      </c>
-      <c r="J73" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="K73" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="74" spans="2:11" x14ac:dyDescent="0.2">
@@ -2180,19 +2180,19 @@
         <v>1000.4</v>
       </c>
       <c r="G74" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="H74" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="I74" t="s">
         <v>54</v>
       </c>
-      <c r="H74" s="1" t="s">
+      <c r="J74" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="I74" t="s">
+      <c r="K74" t="s">
         <v>56</v>
-      </c>
-      <c r="J74" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="K74" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="75" spans="2:11" x14ac:dyDescent="0.2">
@@ -2209,19 +2209,19 @@
         <v>1000.4</v>
       </c>
       <c r="G75" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="H75" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="I75" t="s">
         <v>54</v>
       </c>
-      <c r="H75" s="1" t="s">
+      <c r="J75" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="I75" t="s">
+      <c r="K75" t="s">
         <v>56</v>
-      </c>
-      <c r="J75" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="K75" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="76" spans="2:11" x14ac:dyDescent="0.2">
@@ -2559,16 +2559,16 @@
         <v>250.1</v>
       </c>
       <c r="G98" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="H98" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="J98" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="K98" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="99" spans="2:11" x14ac:dyDescent="0.2">
@@ -2585,16 +2585,16 @@
         <v>1000.2</v>
       </c>
       <c r="G99" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="H99" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="J99" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="K99" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="100" spans="2:11" x14ac:dyDescent="0.2">
@@ -2641,16 +2641,16 @@
         <v>1000.4</v>
       </c>
       <c r="G102" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="H102" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="J102" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="K102" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="103" spans="2:11" x14ac:dyDescent="0.2">
@@ -2667,16 +2667,16 @@
         <v>1000.4</v>
       </c>
       <c r="G103" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="H103" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="J103" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="K103" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="104" spans="2:11" x14ac:dyDescent="0.2">
@@ -2693,16 +2693,16 @@
         <v>1000.4</v>
       </c>
       <c r="G104" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="H104" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="J104" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="K104" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="105" spans="2:11" x14ac:dyDescent="0.2">
@@ -2767,16 +2767,16 @@
         <v>250.1</v>
       </c>
       <c r="G108" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="H108" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="J108" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="K108" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="109" spans="2:11" x14ac:dyDescent="0.2">
@@ -2793,16 +2793,16 @@
         <v>1000.2</v>
       </c>
       <c r="G109" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="H109" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="J109" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="K109" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="110" spans="2:11" x14ac:dyDescent="0.2">
@@ -2849,16 +2849,16 @@
         <v>1000.4</v>
       </c>
       <c r="G112" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="H112" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="J112" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="K112" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="113" spans="1:11" x14ac:dyDescent="0.2">
@@ -2875,16 +2875,16 @@
         <v>1000.4</v>
       </c>
       <c r="G113" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="H113" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="J113" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="K113" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="114" spans="1:11" x14ac:dyDescent="0.2">
@@ -2901,16 +2901,16 @@
         <v>1000.4</v>
       </c>
       <c r="G114" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="H114" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="J114" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="K114" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="115" spans="1:11" x14ac:dyDescent="0.2">
@@ -2927,16 +2927,16 @@
         <v>1000.4</v>
       </c>
       <c r="G115" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="H115" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="J115" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="K115" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="116" spans="1:11" x14ac:dyDescent="0.2">
@@ -2971,16 +2971,16 @@
         <v>250.2</v>
       </c>
       <c r="G117" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="H117" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="J117" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="K117" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="118" spans="1:11" x14ac:dyDescent="0.2">
@@ -2997,16 +2997,16 @@
         <v>250.4</v>
       </c>
       <c r="G118" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="H118" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="J118" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="K118" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="119" spans="1:11" x14ac:dyDescent="0.2">
@@ -3038,16 +3038,16 @@
         <v>250.4</v>
       </c>
       <c r="G120" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="H120" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="J120" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="K120" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="121" spans="1:11" x14ac:dyDescent="0.2">
@@ -3064,16 +3064,16 @@
         <v>250.4</v>
       </c>
       <c r="G121" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="H121" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="J121" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="K121" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="122" spans="1:11" x14ac:dyDescent="0.2">
@@ -3141,7 +3141,7 @@
         <v>250.2</v>
       </c>
       <c r="G125" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="126" spans="1:11" x14ac:dyDescent="0.2">
@@ -3158,7 +3158,7 @@
         <v>250.4</v>
       </c>
       <c r="G126" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="127" spans="1:11" x14ac:dyDescent="0.2">
@@ -3175,7 +3175,7 @@
         <v>250.4</v>
       </c>
       <c r="G127" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="128" spans="1:11" x14ac:dyDescent="0.2">
@@ -3240,7 +3240,7 @@
         <v>250.2</v>
       </c>
       <c r="G131" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="132" spans="2:11" x14ac:dyDescent="0.2">
@@ -3257,7 +3257,7 @@
         <v>250.4</v>
       </c>
       <c r="G132" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="133" spans="2:11" x14ac:dyDescent="0.2">
@@ -3274,7 +3274,7 @@
         <v>250.4</v>
       </c>
       <c r="G133" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="134" spans="2:11" x14ac:dyDescent="0.2">
@@ -3339,7 +3339,7 @@
         <v>250.1</v>
       </c>
       <c r="G137" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="138" spans="2:11" x14ac:dyDescent="0.2">
@@ -3356,7 +3356,7 @@
         <v>250.2</v>
       </c>
       <c r="G138" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="139" spans="2:11" x14ac:dyDescent="0.2">
@@ -3373,7 +3373,7 @@
         <v>250.4</v>
       </c>
       <c r="G139" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="140" spans="2:11" x14ac:dyDescent="0.2">
@@ -3438,10 +3438,10 @@
         <v>1000.2</v>
       </c>
       <c r="G143" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J143" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="144" spans="2:11" x14ac:dyDescent="0.2">
@@ -3458,10 +3458,10 @@
         <v>1000.4</v>
       </c>
       <c r="G144" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J144" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="K144" s="1"/>
     </row>
@@ -3479,10 +3479,10 @@
         <v>1000.2</v>
       </c>
       <c r="G145" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J145" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="K145" s="1"/>
     </row>
@@ -3580,7 +3580,7 @@
         <v>1000.2</v>
       </c>
       <c r="G151" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="152" spans="1:11" x14ac:dyDescent="0.2">
@@ -3597,7 +3597,7 @@
         <v>1000.4</v>
       </c>
       <c r="G152" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I152" s="1"/>
       <c r="J152" s="1"/>
@@ -3617,7 +3617,7 @@
         <v>1000.4</v>
       </c>
       <c r="G153" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I153" s="1"/>
       <c r="J153" s="1"/>
@@ -3636,7 +3636,7 @@
         <v>38</v>
       </c>
       <c r="G154" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I154" s="1"/>
       <c r="J154" s="1"/>
@@ -3655,7 +3655,7 @@
         <v>39</v>
       </c>
       <c r="G155" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I155" s="1"/>
       <c r="J155" s="1"/>
@@ -3674,7 +3674,7 @@
         <v>1000.4</v>
       </c>
       <c r="G156" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I156" s="1"/>
       <c r="J156" s="1"/>
@@ -3693,7 +3693,7 @@
         <v>1000.4</v>
       </c>
       <c r="G157" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I157" s="1"/>
       <c r="J157" s="1"/>
@@ -3712,7 +3712,7 @@
         <v>1000.4</v>
       </c>
       <c r="G158" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I158" s="1"/>
       <c r="J158" s="1"/>
@@ -3731,7 +3731,7 @@
         <v>38</v>
       </c>
       <c r="G159" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I159" s="1"/>
       <c r="J159" s="1"/>
@@ -3750,7 +3750,7 @@
         <v>39</v>
       </c>
       <c r="G160" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I160" s="1"/>
       <c r="J160" s="1"/>
@@ -3844,7 +3844,7 @@
         <v>1000.1</v>
       </c>
       <c r="G166" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="167" spans="1:10" x14ac:dyDescent="0.2">
@@ -3861,7 +3861,7 @@
         <v>1000.2</v>
       </c>
       <c r="G167" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I167" s="1"/>
       <c r="J167" s="1"/>
@@ -3880,7 +3880,7 @@
         <v>1000.2</v>
       </c>
       <c r="G168" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I168" s="1"/>
       <c r="J168" s="1"/>
@@ -3899,7 +3899,7 @@
         <v>1000.4</v>
       </c>
       <c r="G169" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I169" s="1"/>
       <c r="J169" s="1"/>
@@ -3918,7 +3918,7 @@
         <v>1000.4</v>
       </c>
       <c r="G170" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I170" s="1"/>
       <c r="J170" s="1"/>
@@ -3937,7 +3937,7 @@
         <v>1000.2</v>
       </c>
       <c r="G171" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I171" s="1"/>
       <c r="J171" s="1"/>
@@ -3956,7 +3956,7 @@
         <v>1000.2</v>
       </c>
       <c r="G172" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I172" s="1"/>
       <c r="J172" s="1"/>
@@ -3975,7 +3975,7 @@
         <v>1000.4</v>
       </c>
       <c r="G173" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I173" s="1"/>
       <c r="J173" s="1"/>
@@ -3994,7 +3994,7 @@
         <v>1000.4</v>
       </c>
       <c r="G174" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I174" s="1"/>
       <c r="J174" s="1"/>
@@ -4013,7 +4013,7 @@
         <v>1000.4</v>
       </c>
       <c r="G175" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I175" s="1"/>
       <c r="J175" s="1"/>
@@ -4023,7 +4023,7 @@
         <v>41</v>
       </c>
       <c r="B176" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C176" s="1" t="s">
         <v>21</v>
@@ -4054,13 +4054,13 @@
         <v>250.2</v>
       </c>
       <c r="G177" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H177" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="I177" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="178" spans="2:9" x14ac:dyDescent="0.2">
@@ -4091,13 +4091,13 @@
         <v>250.4</v>
       </c>
       <c r="G179" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H179" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="I179" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="180" spans="2:9" x14ac:dyDescent="0.2">
@@ -4114,13 +4114,13 @@
         <v>250.4</v>
       </c>
       <c r="G180" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H180" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="I180" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="181" spans="2:9" x14ac:dyDescent="0.2">
@@ -4151,13 +4151,13 @@
         <v>250.4</v>
       </c>
       <c r="G182" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H182" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="I182" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="183" spans="2:9" x14ac:dyDescent="0.2">
@@ -4174,13 +4174,13 @@
         <v>250.4</v>
       </c>
       <c r="G183" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H183" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="I183" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="184" spans="2:9" x14ac:dyDescent="0.2">
@@ -4211,13 +4211,13 @@
         <v>11</v>
       </c>
       <c r="G185" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H185" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="I185" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="186" spans="2:9" x14ac:dyDescent="0.2">
@@ -4234,18 +4234,18 @@
         <v>12</v>
       </c>
       <c r="G186" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H186" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="I186" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="187" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B187" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C187" s="1" t="s">
         <v>21</v>
@@ -4274,13 +4274,13 @@
         <v>250.2</v>
       </c>
       <c r="G188" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H188" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="I188" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="189" spans="2:9" x14ac:dyDescent="0.2">
@@ -4311,13 +4311,13 @@
         <v>250.4</v>
       </c>
       <c r="G190" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H190" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="I190" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="191" spans="2:9" x14ac:dyDescent="0.2">
@@ -4334,13 +4334,13 @@
         <v>250.4</v>
       </c>
       <c r="G191" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H191" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="I191" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="192" spans="2:9" x14ac:dyDescent="0.2">
@@ -4371,13 +4371,13 @@
         <v>250.4</v>
       </c>
       <c r="G193" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H193" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="I193" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="194" spans="2:9" x14ac:dyDescent="0.2">
@@ -4394,13 +4394,13 @@
         <v>250.4</v>
       </c>
       <c r="G194" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H194" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="I194" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="195" spans="2:9" x14ac:dyDescent="0.2">
@@ -4431,13 +4431,13 @@
         <v>8</v>
       </c>
       <c r="G196" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H196" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="I196" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="197" spans="2:9" x14ac:dyDescent="0.2">
@@ -4454,18 +4454,18 @@
         <v>9</v>
       </c>
       <c r="G197" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H197" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="I197" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="198" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B198" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C198" s="1" t="s">
         <v>21</v>
@@ -4494,13 +4494,13 @@
         <v>250.2</v>
       </c>
       <c r="G199" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H199" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="I199" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="200" spans="2:9" x14ac:dyDescent="0.2">
@@ -4531,13 +4531,13 @@
         <v>250.4</v>
       </c>
       <c r="G201" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H201" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="I201" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="202" spans="2:9" x14ac:dyDescent="0.2">
@@ -4554,13 +4554,13 @@
         <v>250.4</v>
       </c>
       <c r="G202" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H202" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="I202" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="203" spans="2:9" x14ac:dyDescent="0.2">
@@ -4591,13 +4591,13 @@
         <v>250.4</v>
       </c>
       <c r="G204" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H204" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="I204" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="205" spans="2:9" x14ac:dyDescent="0.2">
@@ -4614,13 +4614,13 @@
         <v>250.4</v>
       </c>
       <c r="G205" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H205" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="I205" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="206" spans="2:9" x14ac:dyDescent="0.2">
@@ -4651,13 +4651,13 @@
         <v>8</v>
       </c>
       <c r="G207" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H207" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="I207" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="208" spans="2:9" x14ac:dyDescent="0.2">
@@ -4674,18 +4674,18 @@
         <v>9</v>
       </c>
       <c r="G208" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H208" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="I208" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="209" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B209" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C209" s="1" t="s">
         <v>21</v>
@@ -4714,13 +4714,13 @@
         <v>250.2</v>
       </c>
       <c r="G210" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H210" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="I210" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="211" spans="2:9" x14ac:dyDescent="0.2">
@@ -4751,13 +4751,13 @@
         <v>250.4</v>
       </c>
       <c r="G212" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H212" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="I212" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="213" spans="2:9" x14ac:dyDescent="0.2">
@@ -4774,13 +4774,13 @@
         <v>250.4</v>
       </c>
       <c r="G213" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H213" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="I213" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="214" spans="2:9" x14ac:dyDescent="0.2">
@@ -4811,13 +4811,13 @@
         <v>250.4</v>
       </c>
       <c r="G215" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H215" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="I215" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="216" spans="2:9" x14ac:dyDescent="0.2">
@@ -4834,13 +4834,13 @@
         <v>250.4</v>
       </c>
       <c r="G216" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H216" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="I216" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="217" spans="2:9" x14ac:dyDescent="0.2">
@@ -4871,13 +4871,13 @@
         <v>8</v>
       </c>
       <c r="G218" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H218" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="I218" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="219" spans="2:9" x14ac:dyDescent="0.2">
@@ -4894,13 +4894,13 @@
         <v>9</v>
       </c>
       <c r="G219" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H219" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="I219" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
